--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="108">
   <si>
     <t>Date</t>
   </si>
@@ -169,30 +169,27 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -223,33 +220,30 @@
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Botoşani</t>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Västerås SK</t>
+    <t>Midtjylland</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
     <t>Koper</t>
   </si>
   <si>
@@ -268,12 +262,12 @@
     <t>Unión La Calera</t>
   </si>
   <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
     <t>Tombense</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
@@ -286,33 +280,30 @@
     <t>HJK</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Trelleborg</t>
+    <t>SønderjyskE</t>
   </si>
   <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
     <t>Primorje</t>
   </si>
   <si>
@@ -331,10 +322,10 @@
     <t>Universidad Chile</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Maringá</t>
-  </si>
-  <si>
-    <t>Brusque</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
@@ -710,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -840,13 +831,13 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -861,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M2">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="N2">
-        <v>5.05</v>
+        <v>4.66</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -912,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -936,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL2" s="3">
         <v>45866.4375</v>
@@ -956,13 +947,13 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -977,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L3">
         <v>3.85</v>
@@ -1052,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL3" s="3">
         <v>45866.54166666666</v>
@@ -1072,13 +1063,13 @@
         <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1093,16 +1084,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1168,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL4" s="3">
         <v>45866.54166666666</v>
@@ -1188,13 +1179,13 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1209,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L5">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1284,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL5" s="3">
         <v>45866.54166666666</v>
@@ -1304,13 +1295,13 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1325,16 +1316,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L6">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N6">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1376,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1400,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL6" s="3">
         <v>45866.58333333334</v>
@@ -1417,16 +1408,16 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1441,16 +1432,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L7">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="M7">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1492,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1516,10 +1507,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL7" s="3">
         <v>45866.58333333334</v>
@@ -1533,16 +1524,16 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1557,16 +1548,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L8">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M8">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N8">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1608,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="AC8">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1632,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL8" s="3">
         <v>45866.58333333334</v>
@@ -1652,13 +1643,13 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1673,16 +1664,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L9">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N9">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1724,16 +1715,16 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -1748,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL9" s="3">
         <v>45866.58333333334</v>
@@ -1771,10 +1762,10 @@
         <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1789,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M10">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1840,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AC10">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="AD10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -1864,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL10" s="3">
         <v>45866.58333333334</v>
@@ -1884,13 +1875,13 @@
         <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1905,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1980,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL11" s="3">
         <v>45866.625</v>
@@ -2000,13 +1991,13 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2021,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2072,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2096,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL12" s="3">
         <v>45866.625</v>
@@ -2110,19 +2101,19 @@
         <v>45866</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2137,16 +2128,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L13">
-        <v>1.52</v>
+        <v>3.52</v>
       </c>
       <c r="M13">
-        <v>3.95</v>
+        <v>3.11</v>
       </c>
       <c r="N13">
-        <v>5.2</v>
+        <v>2.12</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2188,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AC13">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2212,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL13" s="3">
-        <v>45866.625</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2226,19 +2217,19 @@
         <v>45866</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2253,16 +2244,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L14">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="N14">
-        <v>2.18</v>
+        <v>3.17</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2304,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2328,13 +2319,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL14" s="3">
-        <v>45866.63541666666</v>
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2342,19 +2333,19 @@
         <v>45866</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2369,16 +2360,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L15">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="M15">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="N15">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2420,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2444,13 +2435,13 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL15" s="3">
-        <v>45866.64583333334</v>
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2458,19 +2449,19 @@
         <v>45866</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2485,16 +2476,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L16">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2560,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL16" s="3">
-        <v>45866.67708333334</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2580,13 +2571,13 @@
         <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2601,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2676,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL17" s="3">
         <v>45866.79166666666</v>
@@ -2690,19 +2681,19 @@
         <v>45866</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2717,16 +2708,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2792,13 +2783,13 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL18" s="3">
-        <v>45866.79166666666</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2809,16 +2800,16 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,16 +2824,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -2908,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL19" s="3">
         <v>45866.8125</v>
@@ -2922,43 +2913,43 @@
         <v>45866</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
         <v>106</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>109</v>
-      </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -2994,16 +2985,16 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3024,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL20" s="3">
-        <v>45866.8125</v>
+        <v>45866.875</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3038,19 +3029,19 @@
         <v>45866</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3065,16 +3056,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L21">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3110,16 +3101,16 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -3140,128 +3131,12 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AK21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AL21" s="3">
-        <v>45866.875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:38">
-      <c r="A22" s="2">
-        <v>45866</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" t="s">
-        <v>87</v>
-      </c>
-      <c r="F22" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" t="s">
-        <v>109</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>110</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL22" s="3">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -157,7 +157,10 @@
     <t>19:30</t>
   </si>
   <si>
-    <t>21:00</t>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:15</t>
   </si>
   <si>
     <t>21:30</t>
@@ -169,28 +172,31 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
@@ -208,6 +214,9 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -220,31 +229,34 @@
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
     <t>Elfsborg</t>
   </si>
   <si>
+    <t>Koper</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Koper</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>Montana</t>
@@ -271,6 +283,9 @@
     <t>Atlanta</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
@@ -280,31 +295,34 @@
     <t>HJK</t>
   </si>
   <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
-    <t>Slavia Sofia</t>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
   </si>
   <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
+    <t>Primorje</t>
+  </si>
+  <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Primorje</t>
+    <t>Honvéd W</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
@@ -329,6 +347,9 @@
   </si>
   <si>
     <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
   </si>
   <si>
     <t>Athletic Club</t>
@@ -701,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:AL23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -828,16 +849,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -852,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L2">
         <v>1.7</v>
@@ -927,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL2" s="3">
         <v>45866.4375</v>
@@ -944,16 +965,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -968,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L3">
         <v>3.85</v>
@@ -1043,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL3" s="3">
         <v>45866.54166666666</v>
@@ -1060,16 +1081,16 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1084,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L4">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1159,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL4" s="3">
         <v>45866.54166666666</v>
@@ -1176,16 +1197,16 @@
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1200,16 +1221,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1251,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1275,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL5" s="3">
         <v>45866.54166666666</v>
@@ -1292,16 +1313,16 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1316,16 +1337,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L6">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
-        <v>3.64</v>
+        <v>4.6</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1367,16 +1388,16 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="AC6">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1391,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL6" s="3">
         <v>45866.58333333334</v>
@@ -1408,16 +1429,16 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1432,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L7">
         <v>3.25</v>
@@ -1483,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1507,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL7" s="3">
         <v>45866.58333333334</v>
@@ -1524,16 +1545,16 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1548,16 +1569,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L8">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="M8">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1599,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AC8">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1623,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL8" s="3">
         <v>45866.58333333334</v>
@@ -1640,16 +1661,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1664,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>2.65</v>
       </c>
       <c r="M9">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1715,16 +1736,16 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC9">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD9">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -1739,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL9" s="3">
         <v>45866.58333333334</v>
@@ -1756,16 +1777,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1780,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L10">
         <v>1.96</v>
@@ -1831,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1855,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL10" s="3">
         <v>45866.58333333334</v>
@@ -1872,16 +1893,16 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1896,16 +1917,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1947,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1971,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL11" s="3">
         <v>45866.625</v>
@@ -1988,16 +2009,16 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2012,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2063,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2087,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL12" s="3">
         <v>45866.625</v>
@@ -2101,19 +2122,19 @@
         <v>45866</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2128,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L13">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2179,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2203,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK13" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL13" s="3">
-        <v>45866.63541666666</v>
+        <v>45866.625</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2217,19 +2238,19 @@
         <v>45866</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2244,16 +2265,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L14">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="M14">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>3.17</v>
+        <v>2.18</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2295,10 +2316,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2319,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL14" s="3">
-        <v>45866.64583333334</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2333,19 +2354,19 @@
         <v>45866</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2360,16 +2381,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L15">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="N15">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2411,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2435,13 +2456,13 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK15" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL15" s="3">
-        <v>45866.67708333334</v>
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2449,19 +2470,19 @@
         <v>45866</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2476,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2551,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL16" s="3">
-        <v>45866.79166666666</v>
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2568,16 +2589,16 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2592,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2637,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB17">
         <v>0</v>
@@ -2667,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK17" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL17" s="3">
         <v>45866.79166666666</v>
@@ -2681,19 +2702,19 @@
         <v>45866</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2708,16 +2729,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L18">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2783,13 +2804,13 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL18" s="3">
-        <v>45866.8125</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2800,16 +2821,16 @@
         <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2824,16 +2845,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L19">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="M19">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -2869,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19">
         <v>0</v>
@@ -2899,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK19" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL19" s="3">
         <v>45866.8125</v>
@@ -2913,19 +2934,19 @@
         <v>45866</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2940,16 +2961,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L20">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="M20">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N20">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -2985,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.87</v>
+        <v>2.23</v>
       </c>
       <c r="AC20">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3015,13 +3036,13 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AK20" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AL20" s="3">
-        <v>45866.875</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3029,114 +3050,346 @@
         <v>45866</v>
       </c>
       <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>113</v>
+      </c>
+      <c r="L21">
+        <v>1.64</v>
+      </c>
+      <c r="M21">
+        <v>3.45</v>
+      </c>
+      <c r="N21">
+        <v>4.9</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>1.65</v>
+      </c>
+      <c r="S21">
+        <v>2.1</v>
+      </c>
+      <c r="T21">
+        <v>3.8</v>
+      </c>
+      <c r="U21">
+        <v>1.22</v>
+      </c>
+      <c r="V21">
+        <v>10</v>
+      </c>
+      <c r="W21">
+        <v>1.02</v>
+      </c>
+      <c r="X21">
+        <v>1.09</v>
+      </c>
+      <c r="Y21">
+        <v>4.75</v>
+      </c>
+      <c r="Z21">
+        <v>1.47</v>
+      </c>
+      <c r="AA21">
+        <v>2.38</v>
+      </c>
+      <c r="AB21">
+        <v>2.87</v>
+      </c>
+      <c r="AC21">
+        <v>1.4</v>
+      </c>
+      <c r="AD21">
+        <v>5.5</v>
+      </c>
+      <c r="AE21">
+        <v>1.07</v>
+      </c>
+      <c r="AF21">
+        <v>2.4</v>
+      </c>
+      <c r="AG21">
+        <v>1.5</v>
+      </c>
+      <c r="AH21">
+        <v>11</v>
+      </c>
+      <c r="AI21">
+        <v>1.03</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>45866.88194444445</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38">
+      <c r="A22" s="2">
+        <v>45866</v>
+      </c>
+      <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" t="s">
-        <v>106</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22">
+        <v>1.65</v>
+      </c>
+      <c r="M22">
+        <v>3.32</v>
+      </c>
+      <c r="N22">
+        <v>4.7</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>1.96</v>
+      </c>
+      <c r="AC22">
+        <v>1.74</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>45866.88541666666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38">
+      <c r="A23" s="2">
+        <v>45866</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>3.35</v>
+      </c>
+      <c r="N23">
+        <v>3.5</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>2.16</v>
+      </c>
+      <c r="AC23">
+        <v>1.64</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,64 +1070,64 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.43</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.43</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.25</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.43</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.43</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>2.63</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M4" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,16 +1778,16 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL23"/>
+  <dimension ref="A1:AL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,64 +806,64 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.4</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,16 +1778,16 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45866.625</v>
+        <v>45866.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45866.63541666666</v>
+        <v>45866.625</v>
       </c>
     </row>
     <row r="15">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>3.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="N15" t="n">
-        <v>3.17</v>
+        <v>2.12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45866.64583333334</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="16">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45866.67708333334</v>
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,22 +2696,22 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45866.79166666666</v>
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="18">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45866.8125</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="20">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3200,58 +3200,58 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>45866.88194444445</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.65</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.96</v>
+        <v>2.87</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45866.88541666666</v>
+        <v>45866.88194444445</v>
       </c>
     </row>
     <row r="23">
@@ -3405,129 +3405,261 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>45866.88541666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>2.21</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>2.83</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>3.19</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC24" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL24" s="3" t="n">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.96</v>
+        <v>3.37</v>
       </c>
       <c r="N2" t="n">
-        <v>4.66</v>
+        <v>4.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -947,43 +947,43 @@
         <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB4" t="n">
         <v>1.5</v>
@@ -998,16 +998,16 @@
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3092,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>1.9</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.84</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2531,31 +2531,31 @@
         <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>7.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.82</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>1.9</v>
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.37</v>
+        <v>3.96</v>
       </c>
       <c r="N2" t="n">
-        <v>4.25</v>
+        <v>4.66</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -695,7 +695,7 @@
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
         <v>3.34</v>
@@ -704,7 +704,7 @@
         <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -713,25 +713,25 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
         <v>2.11</v>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.4</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.82</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1211,43 +1211,43 @@
         <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
@@ -1262,16 +1262,16 @@
         <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.73</v>
       </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="AD9" t="n">
         <v>3.4</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2399,67 +2399,67 @@
         <v>2.12</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2663,49 +2663,49 @@
         <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
         <v>2.05</v>
@@ -2714,16 +2714,16 @@
         <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>5.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3323,25 +3323,25 @@
         <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S22" t="n">
         <v>2.1</v>
       </c>
       <c r="T22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V22" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="Z22" t="n">
         <v>1.47</v>
@@ -3362,28 +3362,28 @@
         <v>2.38</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.5</v>
+        <v>6.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45866.88194444445</v>
+        <v>45866.875</v>
       </c>
     </row>
     <row r="23">
@@ -3455,43 +3455,43 @@
         <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AB23" t="n">
         <v>1.96</v>
@@ -3500,22 +3500,22 @@
         <v>1.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3587,43 +3587,43 @@
         <v>3.19</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB24" t="n">
         <v>2.25</v>
@@ -3632,22 +3632,22 @@
         <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>2.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.96</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>3.96</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>2.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,37 +1466,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -1508,34 +1508,34 @@
         <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.05</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD9" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
         <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P18" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.56</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,73 +3050,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
         <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
         <v>1.02</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,73 +3182,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V21" t="n">
+        <v>10</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.53</v>
       </c>
-      <c r="S21" t="n">
+      <c r="AA21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.38</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI21" t="n">
         <v>1.02</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.96</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.34</v>
-      </c>
       <c r="P5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>3.96</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.22</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AA6" t="n">
         <v>4.2</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AB6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.18</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.07</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.99</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.79</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>6.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,37 +1862,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
@@ -1904,34 +1904,34 @@
         <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,64 +2126,64 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -695,7 +695,7 @@
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
         <v>3.34</v>
@@ -716,10 +716,10 @@
         <v>7.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AB2" t="n">
         <v>2.22</v>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.34</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>6.8</v>
+        <v>4.75</v>
       </c>
       <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>3.96</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.96</v>
+        <v>8.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.7</v>
       </c>
-      <c r="V7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,37 +1598,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1640,34 +1640,34 @@
         <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA10" t="n">
         <v>3.8</v>
       </c>
-      <c r="N10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.75</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,64 +1994,64 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
         <v>2.4</v>
@@ -2423,19 +2423,19 @@
         <v>8.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AB15" t="n">
         <v>2.2</v>
@@ -2444,22 +2444,22 @@
         <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2690,13 +2690,13 @@
         <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AA17" t="n">
         <v>5.25</v>
@@ -2705,7 +2705,7 @@
         <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
         <v>2.05</v>
@@ -2714,16 +2714,16 @@
         <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH17" t="n">
         <v>3.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2804,28 +2804,28 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
         <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>6.95</v>
       </c>
       <c r="Z18" t="n">
         <v>1.52</v>
@@ -2840,16 +2840,16 @@
         <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="n">
         <v>10</v>
@@ -3086,10 +3086,10 @@
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Z20" t="n">
         <v>1.48</v>
@@ -3119,7 +3119,7 @@
         <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
         <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
         <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
         <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
         <v>6.25</v>
@@ -3233,13 +3233,13 @@
         <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AD21" t="n">
         <v>4.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF21" t="n">
         <v>2.38</v>
@@ -3251,7 +3251,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>1.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.7</v>
+        <v>4.75</v>
       </c>
       <c r="Z22" t="n">
         <v>1.47</v>
@@ -3368,7 +3368,7 @@
         <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>6.23</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>1.11</v>
@@ -3380,10 +3380,10 @@
         <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3464,28 +3464,28 @@
         <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Z23" t="n">
         <v>1.27</v>
@@ -3500,7 +3500,7 @@
         <v>1.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE23" t="n">
         <v>1.3</v>
@@ -3509,7 +3509,7 @@
         <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="n">
         <v>6</v>
@@ -3596,34 +3596,34 @@
         <v>2.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
         <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AB24" t="n">
         <v>2.25</v>
@@ -3635,19 +3635,19 @@
         <v>4.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
         <v>1.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.66</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -695,7 +695,7 @@
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
         <v>3.34</v>
@@ -719,13 +719,13 @@
         <v>1.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AD2" t="n">
         <v>4.47</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>2.4</v>
@@ -956,58 +956,58 @@
         <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
         <v>4.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
         <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
         <v>2.34</v>
@@ -1091,22 +1091,22 @@
         <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>6.5</v>
@@ -1121,10 +1121,10 @@
         <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AE5" t="n">
         <v>1.18</v>
@@ -1133,13 +1133,13 @@
         <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="n">
         <v>8.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="M6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.15</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.45</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.73</v>
       </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="AD8" t="n">
         <v>3.4</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,37 +1598,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1637,37 +1637,37 @@
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
         <v>5.5</v>
@@ -1880,10 +1880,10 @@
         <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
@@ -1892,43 +1892,43 @@
         <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.03</v>
+        <v>5.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AI11" t="n">
         <v>1.26</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,64 +2126,64 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.21</v>
+        <v>3.03</v>
       </c>
       <c r="M15" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O15" t="n">
         <v>2.5</v>
@@ -2408,19 +2408,19 @@
         <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
@@ -2429,37 +2429,37 @@
         <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AB15" t="n">
         <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE15" t="n">
         <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N17" t="n">
         <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.55</v>
@@ -2678,10 +2678,10 @@
         <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
         <v>4.33</v>
@@ -2690,40 +2690,40 @@
         <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" t="n">
         <v>5.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.58</v>
@@ -2804,55 +2804,55 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.5</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AE18" t="n">
         <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI18" t="n">
         <v>1.02</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
         <v>2.15</v>
@@ -3068,10 +3068,10 @@
         <v>2.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
         <v>3.4</v>
@@ -3086,40 +3086,40 @@
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
         <v>4</v>
@@ -3200,10 +3200,10 @@
         <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
         <v>3.25</v>
@@ -3212,10 +3212,10 @@
         <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.06</v>
@@ -3224,31 +3224,31 @@
         <v>6.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
         <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AE21" t="n">
         <v>1.12</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AI21" t="n">
         <v>1</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>1.73</v>
@@ -3335,49 +3335,49 @@
         <v>1.66</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T22" t="n">
         <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>6.41</v>
       </c>
       <c r="AE22" t="n">
         <v>1.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
         <v>12</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M23" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>1.8</v>
@@ -3464,58 +3464,58 @@
         <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.8</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
         <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AA23" t="n">
         <v>3.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF23" t="n">
         <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.9</v>
@@ -3596,10 +3596,10 @@
         <v>2.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
         <v>3.4</v>
@@ -3611,40 +3611,40 @@
         <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD24" t="n">
         <v>4.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>1.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI24" t="n">
         <v>1.05</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
         <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
         <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>5.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>3.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,37 +1598,37 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M9" t="n">
         <v>3.3</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1637,37 +1637,37 @@
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.45</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="V11" t="n">
         <v>5.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.98</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.84</v>
+        <v>2.01</v>
       </c>
       <c r="AD11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.42</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.7</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.25</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.53</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AA19" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH19" t="n">
-        <v>4.25</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL24"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7.4</v>
+        <v>4.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.84</v>
+        <v>5.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.11</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,73 +1070,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.71</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.92</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>1.04</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.22</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AA8" t="n">
-        <v>5.98</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.42</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M10" t="n">
         <v>3.3</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
@@ -1769,37 +1769,37 @@
         <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1953,27 +1953,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45866.625</v>
+        <v>45866.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.03</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N15" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45866.63541666666</v>
+        <v>45866.625</v>
       </c>
     </row>
     <row r="16">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.97</v>
+        <v>3.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.73</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2</v>
-      </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45866.64583333334</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="17">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="O17" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45866.67708333334</v>
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>5.25</v>
       </c>
-      <c r="M18" t="n">
+      <c r="AB18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45866.79166666666</v>
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="19">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.66</v>
+        <v>5.25</v>
       </c>
       <c r="M20" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O20" t="n">
         <v>2.6</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="P20" t="n">
-        <v>6.45</v>
+        <v>12.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.5</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.43</v>
+        <v>4.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.75</v>
+        <v>4.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45866.8125</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>2.66</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
         <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AE21" t="n">
         <v>1.12</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AH21" t="n">
-        <v>9.1</v>
+        <v>9.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AD22" t="n">
-        <v>6.41</v>
+        <v>5.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>45866.875</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,73 +3446,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.01</v>
+        <v>2.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.3</v>
+        <v>6.41</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>7.3</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
         <v>1.03</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45866.88541666666</v>
+        <v>45866.875</v>
       </c>
     </row>
     <row r="24">
@@ -3537,129 +3537,261 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL24" s="3" t="n">
+        <v>45866.88541666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>2.34</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>3.3</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>1.9</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>6.5</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>2.4</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1.52</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>2.38</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>3.4</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>10</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>1.04</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y25" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z25" t="n">
         <v>1.42</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AA25" t="n">
         <v>2.7</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB25" t="n">
         <v>2.44</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC25" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AD25" t="n">
         <v>4.7</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AE25" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AF25" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AG25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH25" t="n">
         <v>10</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AI25" t="n">
         <v>1.05</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="n">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.11</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,73 +938,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>1.79</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.92</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>1.04</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>7.4</v>
+        <v>4.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.84</v>
+        <v>5.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.61</v>
+        <v>2.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,40 +1334,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.73</v>
       </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="AD8" t="n">
         <v>3.4</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.8</v>
       </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="Z9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
         <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="O19" t="n">
         <v>1.58</v>
@@ -2936,7 +2936,7 @@
         <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
         <v>2.3</v>
@@ -2948,28 +2948,28 @@
         <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AB19" t="n">
         <v>2.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
         <v>5.1</v>
@@ -2978,13 +2978,13 @@
         <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="AG19" t="n">
         <v>1.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AI19" t="n">
         <v>1.02</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
@@ -3728,34 +3728,34 @@
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
         <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.2</v>
+        <v>6.86</v>
       </c>
       <c r="Z25" t="n">
         <v>1.42</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AB25" t="n">
         <v>2.44</v>
@@ -3767,19 +3767,19 @@
         <v>4.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.34</v>
       </c>
-      <c r="P3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.1</v>
+        <v>4.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.4</v>
       </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.11</v>
+        <v>2.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.2</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.8</v>
       </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AA10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="P12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.98</v>
+        <v>3.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="n">
         <v>4.25</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AI19" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH20" t="n">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
@@ -3479,25 +3479,25 @@
         <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD23" t="n">
         <v>6.41</v>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="O25" t="n">
         <v>1.9</v>
@@ -3758,10 +3758,10 @@
         <v>2.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
         <v>4.7</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4.66</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -692,55 +692,55 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
         <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AI2" t="n">
         <v>1.01</v>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.4</v>
       </c>
-      <c r="P3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>4.75</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.11</v>
+        <v>2.62</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AD3" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.4</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD5" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.1</v>
+        <v>4.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3.64</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.84</v>
+        <v>1.94</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
         <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>12.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH9" t="n">
         <v>3.2</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>2.1</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,37 +1994,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="M12" t="n">
         <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
         <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
@@ -2033,37 +2033,37 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="Z12" t="n">
         <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.03</v>
+        <v>3.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2540,7 +2540,7 @@
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
         <v>2.4</v>
@@ -2552,10 +2552,10 @@
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
@@ -2570,13 +2570,13 @@
         <v>2.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AE16" t="n">
         <v>1.17</v>
@@ -2588,7 +2588,7 @@
         <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AI16" t="n">
         <v>1.04</v>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.55</v>
@@ -2804,28 +2804,28 @@
         <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
         <v>4.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
         <v>1.1</v>
@@ -2834,28 +2834,28 @@
         <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.5</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
+        <v>11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>9</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>9.75</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Z22" t="n">
         <v>1.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>9.1</v>
+        <v>9.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
         <v>1.66</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T23" t="n">
         <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V23" t="n">
         <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="Z23" t="n">
         <v>1.47</v>
@@ -3500,16 +3500,16 @@
         <v>1.36</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.41</v>
+        <v>6.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH23" t="n">
         <v>12</v>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.8</v>
@@ -3596,58 +3596,58 @@
         <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
         <v>1.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3728,16 +3728,16 @@
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T25" t="n">
         <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
         <v>8.5</v>
@@ -3746,13 +3746,13 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.86</v>
+        <v>7.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AA25" t="n">
         <v>2.53</v>
@@ -3764,22 +3764,22 @@
         <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,73 +806,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.84</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="AB3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.92</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
         <v>1.04</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,73 +938,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AI4" t="n">
         <v>1.04</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH6" t="n">
         <v>6.5</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
         <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA11" t="n">
         <v>6</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.2</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V21" t="n">
-        <v>11</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.01</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P22" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V22" t="n">
+        <v>11</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.53</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="AA22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>9</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>9.75</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.34</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AC4" t="n">
         <v>2.4</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD4" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.1</v>
+        <v>4.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.4</v>
       </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.29</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.25</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.75</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AD6" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.3</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="AA8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
         <v>6</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>5</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
@@ -1769,37 +1769,37 @@
         <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
         <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
         <v>5.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>12.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,64 +2258,64 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="N23" t="n">
         <v>4.8</v>
@@ -3464,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="T23" t="n">
         <v>4</v>
@@ -3476,25 +3476,25 @@
         <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y23" t="n">
         <v>4.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
         <v>1.36</v>
@@ -3503,19 +3503,19 @@
         <v>6.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
         <v>12</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45866.875</v>
+        <v>45866.88194444445</v>
       </c>
     </row>
     <row r="24">

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.96</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.66</v>
+        <v>3.83</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -692,7 +692,7 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
         <v>2.53</v>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.28</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.25</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>3.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.4</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.34</v>
-      </c>
       <c r="P5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.5</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AC5" t="n">
         <v>2.4</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD5" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.1</v>
+        <v>4.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH6" t="n">
         <v>5.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AI6" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.27</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,37 +1466,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.4</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
@@ -1505,37 +1505,37 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
         <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.07</v>
+        <v>3.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.75</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AD10" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2543,13 +2543,13 @@
         <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
         <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
         <v>8.4</v>
@@ -2561,7 +2561,7 @@
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="Z16" t="n">
         <v>1.42</v>
@@ -2576,22 +2576,22 @@
         <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
         <v>4.33</v>
@@ -2834,10 +2834,10 @@
         <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
         <v>2.05</v>
@@ -2846,16 +2846,16 @@
         <v>1.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AH18" t="n">
         <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N19" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH21" t="n">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD22" t="n">
         <v>4.4</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.65</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="n">
         <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3596,28 +3596,28 @@
         <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1.35</v>
@@ -3632,19 +3632,19 @@
         <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AF24" t="n">
         <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AI24" t="n">
         <v>1.15</v>
@@ -3740,22 +3740,22 @@
         <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="Z25" t="n">
         <v>1.41</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AB25" t="n">
         <v>2.25</v>
@@ -3764,22 +3764,22 @@
         <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N2" t="n">
-        <v>3.83</v>
+        <v>4.38</v>
       </c>
       <c r="O2" t="n">
         <v>1.57</v>
@@ -692,10 +692,10 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>3.3</v>
@@ -713,19 +713,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AD2" t="n">
         <v>4.2</v>
@@ -734,10 +734,10 @@
         <v>1.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH2" t="n">
         <v>8.5</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>2.4</v>
@@ -956,58 +956,58 @@
         <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
         <v>8.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
         <v>1.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
         <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
         <v>4.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
         <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
         <v>3.85</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.8</v>
-      </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
         <v>2.4</v>
@@ -1088,46 +1088,46 @@
         <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
         <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>1.52</v>
@@ -1136,10 +1136,10 @@
         <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.07</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.99</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.8</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.84</v>
+        <v>3.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>4.65</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,28 +1598,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
         <v>2.75</v>
@@ -1628,7 +1628,7 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1637,37 +1637,37 @@
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
         <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>2.21</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V10" t="n">
         <v>5.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.1</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AH10" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="M16" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2546,52 +2546,52 @@
         <v>2.45</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
         <v>2.68</v>
@@ -3464,7 +3464,7 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
         <v>2.01</v>
@@ -3473,49 +3473,49 @@
         <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>1.67</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
         <v>3.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
         <v>6.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
         <v>12</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>1.8</v>
@@ -3596,16 +3596,16 @@
         <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="T24" t="n">
         <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
         <v>6</v>
@@ -3614,40 +3614,40 @@
         <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
         <v>1.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>3.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
         <v>2.8</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.69</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.34</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.45</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.15</v>
       </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.33</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N10" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N12" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="O18" t="n">
         <v>1.55</v>
@@ -2804,58 +2804,58 @@
         <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
         <v>4.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
         <v>1.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
         <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
         <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.58</v>
@@ -3068,13 +3068,13 @@
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="U20" t="n">
         <v>1.25</v>
@@ -3083,40 +3083,40 @@
         <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
         <v>6.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
         <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI20" t="n">
         <v>1.02</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>4.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P22" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.4</v>
+        <v>5.45</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AH22" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
         <v>1.9</v>
@@ -3731,19 +3731,19 @@
         <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
         <v>3.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>1.1</v>
@@ -3752,34 +3752,34 @@
         <v>7.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AA25" t="n">
         <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH25" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>2.07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>2.99</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
         <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.38</v>
@@ -1364,46 +1364,46 @@
         <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z7" t="n">
         <v>1.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.33</v>
       </c>
-      <c r="M9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.64</v>
+        <v>4.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,76 +3182,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="M21" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>4.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,76 +3314,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>4.25</v>
+        <v>2.69</v>
       </c>
       <c r="O22" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.45</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -157,7 +157,7 @@
     <t>19:30</t>
   </si>
   <si>
-    <t>21:10</t>
+    <t>21:00</t>
   </si>
   <si>
     <t>21:15</t>
@@ -172,22 +172,28 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
@@ -196,9 +202,6 @@
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -229,39 +232,42 @@
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Botoşani</t>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
   </si>
   <si>
     <t>Midtjylland</t>
   </si>
   <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>Odra Opole</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Elfsborg</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
+    <t>Montana</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
@@ -274,12 +280,12 @@
     <t>Unión La Calera</t>
   </si>
   <si>
+    <t>Tombense</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Tombense</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
@@ -295,39 +301,42 @@
     <t>HJK</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>SønderjyskE</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
+    <t>Honvéd W</t>
   </si>
   <si>
     <t>Primorje</t>
   </si>
   <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -340,10 +349,10 @@
     <t>Universidad Chile</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Brusque</t>
-  </si>
-  <si>
-    <t>Maringá</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
@@ -722,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL23"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -852,13 +861,13 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -873,85 +882,85 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L2">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="M2">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="N2">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AB2">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC2">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL2" s="3">
         <v>45866.4375</v>
@@ -968,13 +977,13 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -989,85 +998,85 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
         <v>3.85</v>
       </c>
-      <c r="M3">
-        <v>3.8</v>
-      </c>
       <c r="N3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB3">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
         <v>2.4</v>
       </c>
       <c r="AD3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE3">
         <v>1.55</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL3" s="3">
         <v>45866.54166666666</v>
@@ -1084,13 +1093,13 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1105,85 +1114,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL4" s="3">
         <v>45866.54166666666</v>
@@ -1200,13 +1209,13 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1221,85 +1230,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L5">
-        <v>1.79</v>
+        <v>2.85</v>
       </c>
       <c r="M5">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL5" s="3">
         <v>45866.54166666666</v>
@@ -1316,13 +1325,13 @@
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1337,43 +1346,43 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="M6">
-        <v>4.6</v>
+        <v>3.64</v>
       </c>
       <c r="N6">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -1388,23 +1397,23 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1.8</v>
+      </c>
+      <c r="AG6">
         <v>1.95</v>
       </c>
-      <c r="AE6">
-        <v>1.7</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
       <c r="AH6">
         <v>0</v>
       </c>
@@ -1412,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL6" s="3">
         <v>45866.58333333334</v>
@@ -1432,13 +1441,13 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1453,16 +1462,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L7">
-        <v>3.25</v>
+        <v>2.07</v>
       </c>
       <c r="M7">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N7">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1504,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1528,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL7" s="3">
         <v>45866.58333333334</v>
@@ -1551,10 +1560,10 @@
         <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1569,85 +1578,85 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L8">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
+        <v>4.7</v>
+      </c>
+      <c r="N8">
+        <v>6.2</v>
+      </c>
+      <c r="O8">
+        <v>1.4</v>
+      </c>
+      <c r="P8">
+        <v>17</v>
+      </c>
+      <c r="Q8">
+        <v>2.75</v>
+      </c>
+      <c r="R8">
+        <v>1.18</v>
+      </c>
+      <c r="S8">
         <v>3.8</v>
       </c>
-      <c r="N8">
-        <v>4.5</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
       <c r="T8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AB8">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AC8">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL8" s="3">
         <v>45866.58333333334</v>
@@ -1661,16 +1670,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1685,85 +1694,85 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L9">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M9">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N9">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB9">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL9" s="3">
         <v>45866.58333333334</v>
@@ -1777,16 +1786,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1801,85 +1810,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L10">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="M10">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N10">
-        <v>3.11</v>
+        <v>2.01</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL10" s="3">
         <v>45866.58333333334</v>
@@ -1890,19 +1899,19 @@
         <v>45866</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1917,88 +1926,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="M11">
-        <v>3.95</v>
+        <v>3.39</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL11" s="3">
-        <v>45866.625</v>
+        <v>45866.58333333334</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2006,19 +2015,19 @@
         <v>45866</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2033,88 +2042,88 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL12" s="3">
-        <v>45866.625</v>
+        <v>45866.58333333334</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2125,16 +2134,16 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2149,25 +2158,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2200,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2224,10 +2233,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL13" s="3">
         <v>45866.625</v>
@@ -2238,19 +2247,19 @@
         <v>45866</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2265,16 +2274,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L14">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N14">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2316,16 +2325,16 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2340,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL14" s="3">
-        <v>45866.63541666666</v>
+        <v>45866.625</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2354,19 +2363,19 @@
         <v>45866</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2381,88 +2390,88 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L15">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="M15">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="N15">
-        <v>3.17</v>
+        <v>1.81</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB15">
+        <v>2.28</v>
+      </c>
+      <c r="AC15">
+        <v>1.57</v>
+      </c>
+      <c r="AD15">
+        <v>4.05</v>
+      </c>
+      <c r="AE15">
+        <v>1.22</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AG15">
         <v>1.8</v>
       </c>
-      <c r="AC15">
-        <v>1.9</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
       <c r="AH15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL15" s="3">
-        <v>45866.64583333334</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2470,19 +2479,19 @@
         <v>45866</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2497,16 +2506,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L16">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2572,13 +2581,13 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK16" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL16" s="3">
-        <v>45866.67708333334</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2586,10 +2595,10 @@
         <v>45866</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2598,7 +2607,7 @@
         <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2613,43 +2622,43 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L17">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="M17">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="N17">
-        <v>5.4</v>
+        <v>3.17</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>0</v>
@@ -2658,16 +2667,16 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -2676,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2688,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL17" s="3">
-        <v>45866.79166666666</v>
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2702,19 +2711,19 @@
         <v>45866</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2729,88 +2738,88 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL18" s="3">
-        <v>45866.79166666666</v>
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2818,19 +2827,19 @@
         <v>45866</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2845,88 +2854,88 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L19">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="M19">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N19">
-        <v>4.43</v>
+        <v>5.1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z19">
+        <v>1.52</v>
+      </c>
+      <c r="AA19">
+        <v>2.4</v>
+      </c>
+      <c r="AB19">
+        <v>2.3</v>
+      </c>
+      <c r="AC19">
+        <v>1.5</v>
+      </c>
+      <c r="AD19">
+        <v>5.1</v>
+      </c>
+      <c r="AE19">
+        <v>1.14</v>
+      </c>
+      <c r="AF19">
+        <v>2.37</v>
+      </c>
+      <c r="AG19">
         <v>1.54</v>
       </c>
-      <c r="AA19">
-        <v>2.28</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
       <c r="AH19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL19" s="3">
-        <v>45866.8125</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2934,19 +2943,19 @@
         <v>45866</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
         <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2961,88 +2970,88 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L20">
-        <v>2.14</v>
+        <v>5.25</v>
       </c>
       <c r="M20">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N20">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB20">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL20" s="3">
-        <v>45866.8125</v>
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3050,19 +3059,19 @@
         <v>45866</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
         <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3077,88 +3086,88 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L21">
-        <v>1.64</v>
+        <v>2.55</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N21">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="S21">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
+        <v>1.1</v>
+      </c>
+      <c r="Y21">
+        <v>5.8</v>
+      </c>
+      <c r="Z21">
+        <v>1.48</v>
+      </c>
+      <c r="AA21">
+        <v>2.46</v>
+      </c>
+      <c r="AB21">
+        <v>2.2</v>
+      </c>
+      <c r="AC21">
+        <v>1.55</v>
+      </c>
+      <c r="AD21">
+        <v>4.3</v>
+      </c>
+      <c r="AE21">
+        <v>1.17</v>
+      </c>
+      <c r="AF21">
+        <v>2</v>
+      </c>
+      <c r="AG21">
+        <v>1.7</v>
+      </c>
+      <c r="AH21">
+        <v>10.5</v>
+      </c>
+      <c r="AI21">
         <v>1.02</v>
       </c>
-      <c r="X21">
-        <v>1.09</v>
-      </c>
-      <c r="Y21">
-        <v>4.75</v>
-      </c>
-      <c r="Z21">
-        <v>1.47</v>
-      </c>
-      <c r="AA21">
-        <v>2.38</v>
-      </c>
-      <c r="AB21">
-        <v>2.87</v>
-      </c>
-      <c r="AC21">
-        <v>1.4</v>
-      </c>
-      <c r="AD21">
-        <v>5.5</v>
-      </c>
-      <c r="AE21">
-        <v>1.07</v>
-      </c>
-      <c r="AF21">
-        <v>2.4</v>
-      </c>
-      <c r="AG21">
-        <v>1.5</v>
-      </c>
-      <c r="AH21">
-        <v>11</v>
-      </c>
-      <c r="AI21">
-        <v>1.03</v>
-      </c>
       <c r="AJ21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL21" s="3">
-        <v>45866.88194444445</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -3166,19 +3175,19 @@
         <v>45866</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
         <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3193,88 +3202,88 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L22">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="M22">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="N22">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AL22" s="3">
-        <v>45866.88541666666</v>
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="23" spans="1:38">
@@ -3282,19 +3291,19 @@
         <v>45866</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
         <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3309,87 +3318,319 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="M23">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="AC23">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ23" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>45866.875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38">
+      <c r="A24" s="2">
+        <v>45866</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s">
         <v>114</v>
       </c>
-      <c r="AK23" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L24">
+        <v>2.04</v>
+      </c>
+      <c r="M24">
+        <v>3.45</v>
+      </c>
+      <c r="N24">
+        <v>2.96</v>
+      </c>
+      <c r="O24">
+        <v>1.8</v>
+      </c>
+      <c r="P24">
+        <v>10</v>
+      </c>
+      <c r="Q24">
+        <v>2.3</v>
+      </c>
+      <c r="R24">
+        <v>1.33</v>
+      </c>
+      <c r="S24">
+        <v>2.9</v>
+      </c>
+      <c r="T24">
+        <v>2.62</v>
+      </c>
+      <c r="U24">
+        <v>1.4</v>
+      </c>
+      <c r="V24">
+        <v>6.5</v>
+      </c>
+      <c r="W24">
+        <v>1.09</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z24">
+        <v>1.35</v>
+      </c>
+      <c r="AA24">
+        <v>3.01</v>
+      </c>
+      <c r="AB24">
+        <v>1.85</v>
+      </c>
+      <c r="AC24">
+        <v>1.91</v>
+      </c>
+      <c r="AD24">
+        <v>3</v>
+      </c>
+      <c r="AE24">
+        <v>1.33</v>
+      </c>
+      <c r="AF24">
+        <v>1.65</v>
+      </c>
+      <c r="AG24">
+        <v>2.1</v>
+      </c>
+      <c r="AH24">
+        <v>5.75</v>
+      </c>
+      <c r="AI24">
+        <v>1.13</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>45866.88541666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38">
+      <c r="A25" s="2">
+        <v>45866</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>116</v>
+      </c>
+      <c r="L25">
+        <v>2.21</v>
+      </c>
+      <c r="M25">
+        <v>2.83</v>
+      </c>
+      <c r="N25">
+        <v>3.19</v>
+      </c>
+      <c r="O25">
+        <v>1.9</v>
+      </c>
+      <c r="P25">
+        <v>6.5</v>
+      </c>
+      <c r="Q25">
+        <v>2.4</v>
+      </c>
+      <c r="R25">
+        <v>1.52</v>
+      </c>
+      <c r="S25">
+        <v>2.38</v>
+      </c>
+      <c r="T25">
+        <v>3.4</v>
+      </c>
+      <c r="U25">
+        <v>1.27</v>
+      </c>
+      <c r="V25">
+        <v>8.5</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.1</v>
+      </c>
+      <c r="Y25">
+        <v>7.5</v>
+      </c>
+      <c r="Z25">
+        <v>1.5</v>
+      </c>
+      <c r="AA25">
+        <v>2.68</v>
+      </c>
+      <c r="AB25">
+        <v>2.25</v>
+      </c>
+      <c r="AC25">
+        <v>1.5</v>
+      </c>
+      <c r="AD25">
+        <v>4.5</v>
+      </c>
+      <c r="AE25">
+        <v>1.17</v>
+      </c>
+      <c r="AF25">
+        <v>2.05</v>
+      </c>
+      <c r="AG25">
+        <v>1.65</v>
+      </c>
+      <c r="AH25">
+        <v>9</v>
+      </c>
+      <c r="AI25">
+        <v>1.01</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -157,7 +157,7 @@
     <t>19:30</t>
   </si>
   <si>
-    <t>21:00</t>
+    <t>21:10</t>
   </si>
   <si>
     <t>21:15</t>
@@ -169,28 +169,31 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
+    <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Hungary NB II</t>
@@ -199,18 +202,15 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Faroe Islands Faroe Islands Premier League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -229,31 +229,34 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
   </si>
   <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
+    <t>B36</t>
   </si>
   <si>
     <t>Videoton</t>
@@ -265,21 +268,18 @@
     <t>Montana</t>
   </si>
   <si>
-    <t>B36</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Unión La Calera</t>
-  </si>
-  <si>
     <t>Tombense</t>
   </si>
   <si>
@@ -298,31 +298,34 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>HJK</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Varberg</t>
   </si>
   <si>
     <t>Trelleborg</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
   </si>
   <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Varberg</t>
+    <t>TB</t>
   </si>
   <si>
     <t>Honvéd W</t>
@@ -334,19 +337,16 @@
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>TB</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
   </si>
   <si>
     <t>Maringá</t>
@@ -885,13 +885,13 @@
         <v>116</v>
       </c>
       <c r="L2">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M2">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="O2">
         <v>1.57</v>
@@ -933,10 +933,10 @@
         <v>2.72</v>
       </c>
       <c r="AB2">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AC2">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AD2">
         <v>4.2</v>
@@ -977,7 +977,7 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>71</v>
@@ -1001,76 +1001,76 @@
         <v>116</v>
       </c>
       <c r="L3">
+        <v>1.79</v>
+      </c>
+      <c r="M3">
+        <v>3.21</v>
+      </c>
+      <c r="N3">
         <v>4</v>
       </c>
-      <c r="M3">
-        <v>3.85</v>
-      </c>
-      <c r="N3">
-        <v>1.7</v>
-      </c>
       <c r="O3">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V3">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="Z3">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AD3">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AE3">
-        <v>1.55</v>
+        <v>1.21</v>
       </c>
       <c r="AF3">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI3">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
         <v>117</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="P4">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q4">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V4">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AA4">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD4">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1209,7 +1209,7 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -1233,76 +1233,76 @@
         <v>116</v>
       </c>
       <c r="L5">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="M5">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="O5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="P5">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="V5">
-        <v>8.300000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AA5">
-        <v>2.6</v>
+        <v>4.97</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC5">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AD5">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AH5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AI5">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>117</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
@@ -1349,52 +1349,52 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="M6">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="O6">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V6">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB6">
         <v>1.76</v>
@@ -1403,22 +1403,22 @@
         <v>1.94</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1441,7 +1441,7 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>75</v>
@@ -1465,76 +1465,76 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M7">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N7">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB7">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC7">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1554,10 +1554,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -1581,76 +1581,76 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="M8">
-        <v>4.7</v>
+        <v>3.64</v>
       </c>
       <c r="N8">
-        <v>6.2</v>
+        <v>4.33</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
+        <v>3.25</v>
+      </c>
+      <c r="T8">
+        <v>2.63</v>
+      </c>
+      <c r="U8">
+        <v>1.44</v>
+      </c>
+      <c r="V8">
+        <v>6.5</v>
+      </c>
+      <c r="W8">
+        <v>1.11</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>10</v>
+      </c>
+      <c r="Z8">
+        <v>1.28</v>
+      </c>
+      <c r="AA8">
         <v>3.8</v>
       </c>
-      <c r="T8">
-        <v>2</v>
-      </c>
-      <c r="U8">
-        <v>1.7</v>
-      </c>
-      <c r="V8">
-        <v>4</v>
-      </c>
-      <c r="W8">
-        <v>1.15</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>17</v>
-      </c>
-      <c r="Z8">
-        <v>1.13</v>
-      </c>
-      <c r="AA8">
-        <v>5.7</v>
-      </c>
       <c r="AB8">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="AD8">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AH8">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="AI8">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,7 +1670,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>69</v>
@@ -1786,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>68</v>
@@ -1816,10 +1816,10 @@
         <v>3.25</v>
       </c>
       <c r="M10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N10">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
         <v>2.3</v>
@@ -1861,10 +1861,10 @@
         <v>3.2</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD10">
         <v>3.34</v>
@@ -1902,16 +1902,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,76 +1929,76 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="M11">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="O11">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD11">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,10 +2018,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N12">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O12">
+        <v>1.4</v>
+      </c>
+      <c r="P12">
+        <v>17</v>
+      </c>
+      <c r="Q12">
+        <v>2.75</v>
+      </c>
+      <c r="R12">
+        <v>1.18</v>
+      </c>
+      <c r="S12">
+        <v>3.8</v>
+      </c>
+      <c r="T12">
         <v>2</v>
       </c>
-      <c r="P12">
-        <v>9</v>
-      </c>
-      <c r="Q12">
-        <v>2.05</v>
-      </c>
-      <c r="R12">
-        <v>1.38</v>
-      </c>
-      <c r="S12">
-        <v>2.8</v>
-      </c>
-      <c r="T12">
-        <v>2.75</v>
-      </c>
       <c r="U12">
+        <v>1.7</v>
+      </c>
+      <c r="V12">
+        <v>4</v>
+      </c>
+      <c r="W12">
+        <v>1.15</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>17</v>
+      </c>
+      <c r="Z12">
+        <v>1.13</v>
+      </c>
+      <c r="AA12">
+        <v>5.7</v>
+      </c>
+      <c r="AB12">
         <v>1.4</v>
       </c>
-      <c r="V12">
-        <v>7.5</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.06</v>
-      </c>
-      <c r="Y12">
-        <v>9</v>
-      </c>
-      <c r="Z12">
+      <c r="AC12">
+        <v>2.82</v>
+      </c>
+      <c r="AD12">
+        <v>1.95</v>
+      </c>
+      <c r="AE12">
+        <v>1.7</v>
+      </c>
+      <c r="AF12">
+        <v>1.57</v>
+      </c>
+      <c r="AG12">
+        <v>2.37</v>
+      </c>
+      <c r="AH12">
+        <v>3.4</v>
+      </c>
+      <c r="AI12">
         <v>1.3</v>
-      </c>
-      <c r="AA12">
-        <v>3.45</v>
-      </c>
-      <c r="AB12">
-        <v>1.92</v>
-      </c>
-      <c r="AC12">
-        <v>1.78</v>
-      </c>
-      <c r="AD12">
-        <v>3.4</v>
-      </c>
-      <c r="AE12">
-        <v>1.33</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2.05</v>
-      </c>
-      <c r="AH12">
-        <v>6.5</v>
-      </c>
-      <c r="AI12">
-        <v>1.11</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2137,7 +2137,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
@@ -2161,22 +2161,22 @@
         <v>116</v>
       </c>
       <c r="L13">
-        <v>2.3</v>
+        <v>1.15</v>
       </c>
       <c r="M13">
-        <v>3.1</v>
+        <v>7.17</v>
       </c>
       <c r="N13">
-        <v>2.8</v>
+        <v>10.17</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AC13">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2277,22 +2277,22 @@
         <v>116</v>
       </c>
       <c r="L14">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="M14">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2325,16 +2325,16 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>45866</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -2393,76 +2393,76 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="M15">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="N15">
-        <v>1.81</v>
+        <v>4.7</v>
       </c>
       <c r="O15">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AF15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2471,7 +2471,7 @@
         <v>117</v>
       </c>
       <c r="AL15" s="3">
-        <v>45866.63541666666</v>
+        <v>45866.625</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2482,10 +2482,10 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
@@ -2509,76 +2509,76 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ16" t="s">
         <v>117</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2741,13 +2741,13 @@
         <v>116</v>
       </c>
       <c r="L18">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M18">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N18">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="O18">
         <v>1.55</v>
@@ -2765,10 +2765,10 @@
         <v>4</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V18">
         <v>4.33</v>
@@ -2786,31 +2786,31 @@
         <v>1.1</v>
       </c>
       <c r="AA18">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AB18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC18">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AD18">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AE18">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AF18">
         <v>1.47</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AH18">
         <v>3.4</v>
       </c>
       <c r="AI18">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="s">
         <v>117</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M19">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N19">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P19">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R19">
+        <v>1.3</v>
+      </c>
+      <c r="S19">
+        <v>3.4</v>
+      </c>
+      <c r="T19">
+        <v>2.5</v>
+      </c>
+      <c r="U19">
         <v>1.5</v>
       </c>
-      <c r="S19">
-        <v>2.4</v>
-      </c>
-      <c r="T19">
-        <v>3.4</v>
-      </c>
-      <c r="U19">
-        <v>1.25</v>
-      </c>
       <c r="V19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W19">
+        <v>1.13</v>
+      </c>
+      <c r="X19">
         <v>1.04</v>
       </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
       <c r="Y19">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA19">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB19">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
+        <v>2.1</v>
+      </c>
+      <c r="AD19">
+        <v>2.5</v>
+      </c>
+      <c r="AE19">
         <v>1.5</v>
       </c>
-      <c r="AD19">
-        <v>5.1</v>
-      </c>
-      <c r="AE19">
-        <v>1.14</v>
-      </c>
       <c r="AF19">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AH19">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI19">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O20">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
+        <v>2.4</v>
+      </c>
+      <c r="T20">
         <v>3.4</v>
       </c>
-      <c r="T20">
-        <v>2.5</v>
-      </c>
       <c r="U20">
+        <v>1.25</v>
+      </c>
+      <c r="V20">
+        <v>9</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.05</v>
+      </c>
+      <c r="Y20">
+        <v>6.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.52</v>
+      </c>
+      <c r="AA20">
+        <v>2.4</v>
+      </c>
+      <c r="AB20">
+        <v>2.3</v>
+      </c>
+      <c r="AC20">
         <v>1.5</v>
       </c>
-      <c r="V20">
-        <v>6</v>
-      </c>
-      <c r="W20">
-        <v>1.13</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>9.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.2</v>
-      </c>
-      <c r="AA20">
-        <v>4.33</v>
-      </c>
-      <c r="AB20">
-        <v>1.7</v>
-      </c>
-      <c r="AC20">
-        <v>2.1</v>
-      </c>
       <c r="AD20">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AH20">
-        <v>4.25</v>
+        <v>11.5</v>
       </c>
       <c r="AI20">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3089,13 +3089,13 @@
         <v>116</v>
       </c>
       <c r="L21">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="M21">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="O21">
         <v>2.15</v>
@@ -3110,13 +3110,13 @@
         <v>1.51</v>
       </c>
       <c r="S21">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="T21">
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -3143,7 +3143,7 @@
         <v>1.55</v>
       </c>
       <c r="AD21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE21">
         <v>1.17</v>
@@ -3155,10 +3155,10 @@
         <v>1.7</v>
       </c>
       <c r="AH21">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ21" t="s">
         <v>117</v>
@@ -3205,13 +3205,13 @@
         <v>116</v>
       </c>
       <c r="L22">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
         <v>1.67</v>
@@ -3223,13 +3223,13 @@
         <v>2.82</v>
       </c>
       <c r="R22">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S22">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U22">
         <v>1.22</v>
@@ -3238,13 +3238,13 @@
         <v>11</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Z22">
         <v>1.53</v>
@@ -3253,28 +3253,28 @@
         <v>2.25</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AC22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD22">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AE22">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>2.35</v>
       </c>
       <c r="AG22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH22">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AI22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="s">
         <v>117</v>
@@ -3399,7 +3399,7 @@
         <v>117</v>
       </c>
       <c r="AL23" s="3">
-        <v>45866.875</v>
+        <v>45866.88194444445</v>
       </c>
     </row>
     <row r="24" spans="1:38">
@@ -3437,13 +3437,13 @@
         <v>116</v>
       </c>
       <c r="L24">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="M24">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="N24">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="O24">
         <v>1.8</v>
@@ -3455,28 +3455,28 @@
         <v>2.3</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="T24">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V24">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>1.35</v>
@@ -3485,28 +3485,28 @@
         <v>3.01</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AD24">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH24">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AI24">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ24" t="s">
         <v>117</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3574,7 +3574,7 @@
         <v>1.52</v>
       </c>
       <c r="S25">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="T25">
         <v>3.4</v>
@@ -3586,19 +3586,19 @@
         <v>8.5</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z25">
         <v>1.5</v>
       </c>
       <c r="AA25">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AB25">
         <v>2.25</v>
@@ -3610,19 +3610,19 @@
         <v>4.5</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
         <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH25">
         <v>9</v>
       </c>
       <c r="AI25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="s">
         <v>117</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -169,48 +169,48 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -229,57 +229,57 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Montana</t>
   </si>
   <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Tombense</t>
   </si>
   <si>
@@ -298,55 +298,55 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
     <t>HJK</t>
   </si>
   <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
+    <t>Primorje</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Primorje</t>
-  </si>
-  <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
   </si>
   <si>
     <t>Maringá</t>
@@ -1001,76 +1001,76 @@
         <v>116</v>
       </c>
       <c r="L3">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M3">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="P3">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="T3">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V3">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Z3">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AA3">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD3">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE3">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
         <v>117</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M4">
+        <v>3.21</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4">
+        <v>1.66</v>
+      </c>
+      <c r="P4">
+        <v>7.5</v>
+      </c>
+      <c r="Q4">
+        <v>2.71</v>
+      </c>
+      <c r="R4">
+        <v>1.44</v>
+      </c>
+      <c r="S4">
+        <v>2.59</v>
+      </c>
+      <c r="T4">
+        <v>3.04</v>
+      </c>
+      <c r="U4">
+        <v>1.33</v>
+      </c>
+      <c r="V4">
+        <v>7.4</v>
+      </c>
+      <c r="W4">
+        <v>1.03</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>7.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.33</v>
+      </c>
+      <c r="AA4">
         <v>2.84</v>
       </c>
-      <c r="N4">
-        <v>2.4</v>
-      </c>
-      <c r="O4">
-        <v>2.34</v>
-      </c>
-      <c r="P4">
-        <v>6.4</v>
-      </c>
-      <c r="Q4">
+      <c r="AB4">
+        <v>2.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.61</v>
+      </c>
+      <c r="AD4">
+        <v>3.6</v>
+      </c>
+      <c r="AE4">
+        <v>1.21</v>
+      </c>
+      <c r="AF4">
         <v>1.92</v>
       </c>
-      <c r="R4">
-        <v>1.45</v>
-      </c>
-      <c r="S4">
-        <v>2.45</v>
-      </c>
-      <c r="T4">
-        <v>3.3</v>
-      </c>
-      <c r="U4">
-        <v>1.28</v>
-      </c>
-      <c r="V4">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W4">
-        <v>1.02</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>8</v>
-      </c>
-      <c r="Z4">
-        <v>1.46</v>
-      </c>
-      <c r="AA4">
-        <v>2.6</v>
-      </c>
-      <c r="AB4">
-        <v>2.25</v>
-      </c>
-      <c r="AC4">
-        <v>1.53</v>
-      </c>
-      <c r="AD4">
-        <v>4.33</v>
-      </c>
-      <c r="AE4">
-        <v>1.15</v>
-      </c>
-      <c r="AF4">
-        <v>2</v>
-      </c>
       <c r="AG4">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI4">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
@@ -1349,40 +1349,40 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="M6">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="N6">
-        <v>2.99</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="P6">
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.05</v>
@@ -1391,10 +1391,10 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AA6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB6">
         <v>1.76</v>
@@ -1403,22 +1403,22 @@
         <v>1.94</v>
       </c>
       <c r="AD6">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AE6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH6">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1441,7 +1441,7 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>75</v>
@@ -1465,76 +1465,76 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N7">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
+        <v>1.4</v>
+      </c>
+      <c r="P7">
+        <v>17</v>
+      </c>
+      <c r="Q7">
+        <v>2.75</v>
+      </c>
+      <c r="R7">
+        <v>1.18</v>
+      </c>
+      <c r="S7">
+        <v>3.8</v>
+      </c>
+      <c r="T7">
         <v>2</v>
       </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>2.05</v>
-      </c>
-      <c r="R7">
-        <v>1.38</v>
-      </c>
-      <c r="S7">
-        <v>2.8</v>
-      </c>
-      <c r="T7">
-        <v>2.75</v>
-      </c>
       <c r="U7">
+        <v>1.7</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
+      </c>
+      <c r="W7">
+        <v>1.15</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>17</v>
+      </c>
+      <c r="Z7">
+        <v>1.13</v>
+      </c>
+      <c r="AA7">
+        <v>5.7</v>
+      </c>
+      <c r="AB7">
         <v>1.4</v>
       </c>
-      <c r="V7">
-        <v>7.5</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.06</v>
-      </c>
-      <c r="Y7">
-        <v>9</v>
-      </c>
-      <c r="Z7">
+      <c r="AC7">
+        <v>2.82</v>
+      </c>
+      <c r="AD7">
+        <v>1.95</v>
+      </c>
+      <c r="AE7">
+        <v>1.7</v>
+      </c>
+      <c r="AF7">
+        <v>1.57</v>
+      </c>
+      <c r="AG7">
+        <v>2.37</v>
+      </c>
+      <c r="AH7">
+        <v>3.4</v>
+      </c>
+      <c r="AI7">
         <v>1.3</v>
-      </c>
-      <c r="AA7">
-        <v>3.45</v>
-      </c>
-      <c r="AB7">
-        <v>1.92</v>
-      </c>
-      <c r="AC7">
-        <v>1.78</v>
-      </c>
-      <c r="AD7">
-        <v>3.4</v>
-      </c>
-      <c r="AE7">
-        <v>1.33</v>
-      </c>
-      <c r="AF7">
-        <v>1.67</v>
-      </c>
-      <c r="AG7">
-        <v>2.05</v>
-      </c>
-      <c r="AH7">
-        <v>6.5</v>
-      </c>
-      <c r="AI7">
-        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1554,10 +1554,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -1581,76 +1581,76 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="M8">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="N8">
-        <v>4.33</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="T8">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V8">
         <v>6.5</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE8">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AI8">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,10 +1670,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
         <v>77</v>
@@ -1697,40 +1697,40 @@
         <v>116</v>
       </c>
       <c r="L9">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="M9">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="N9">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="O9">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P9">
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.05</v>
@@ -1739,22 +1739,22 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AA9">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB9">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD9">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AE9">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
         <v>1.62</v>
@@ -1763,10 +1763,10 @@
         <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AI9">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="s">
         <v>117</v>
@@ -1786,10 +1786,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
         <v>78</v>
@@ -1813,76 +1813,76 @@
         <v>116</v>
       </c>
       <c r="L10">
-        <v>3.25</v>
+        <v>1.96</v>
       </c>
       <c r="M10">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="N10">
-        <v>2.12</v>
+        <v>3.11</v>
       </c>
       <c r="O10">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="P10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA10">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AC10">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AD10">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI10">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="s">
         <v>117</v>
@@ -1905,13 +1905,13 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,76 +1929,76 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M11">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB11">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC11">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,16 +2018,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M12">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N12">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD12">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2137,7 +2137,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
@@ -2161,13 +2161,13 @@
         <v>116</v>
       </c>
       <c r="L13">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="M13">
-        <v>7.17</v>
+        <v>3.98</v>
       </c>
       <c r="N13">
-        <v>10.17</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>45866</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -2393,76 +2393,76 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>1.52</v>
+        <v>3.21</v>
       </c>
       <c r="M15">
-        <v>3.98</v>
+        <v>2.98</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB15">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AD15">
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="AE15">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2471,7 +2471,7 @@
         <v>117</v>
       </c>
       <c r="AL15" s="3">
-        <v>45866.625</v>
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2482,10 +2482,10 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
@@ -2509,76 +2509,76 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>3.21</v>
+        <v>1.1</v>
       </c>
       <c r="M16">
-        <v>2.98</v>
+        <v>7.5</v>
       </c>
       <c r="N16">
-        <v>2.12</v>
+        <v>11.25</v>
       </c>
       <c r="O16">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>7.1</v>
+        <v>26</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>3.28</v>
+      </c>
+      <c r="W16">
         <v>1.3</v>
       </c>
-      <c r="V16">
-        <v>6.7</v>
-      </c>
-      <c r="W16">
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>41</v>
+      </c>
+      <c r="Z16">
         <v>1.05</v>
       </c>
-      <c r="X16">
-        <v>1.08</v>
-      </c>
-      <c r="Y16">
-        <v>7</v>
-      </c>
-      <c r="Z16">
-        <v>1.41</v>
-      </c>
       <c r="AA16">
-        <v>2.67</v>
+        <v>8</v>
       </c>
       <c r="AB16">
+        <v>1.25</v>
+      </c>
+      <c r="AC16">
+        <v>3.6</v>
+      </c>
+      <c r="AD16">
+        <v>1.6</v>
+      </c>
+      <c r="AE16">
         <v>2.2</v>
       </c>
-      <c r="AC16">
-        <v>1.55</v>
-      </c>
-      <c r="AD16">
-        <v>4.05</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
       <c r="AF16">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AH16">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="AI16">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ16" t="s">
         <v>117</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>5.25</v>
+        <v>1.65</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="R19">
         <v>1.53</v>
       </c>
-      <c r="R19">
-        <v>1.3</v>
-      </c>
       <c r="S19">
+        <v>2.39</v>
+      </c>
+      <c r="T19">
         <v>3.4</v>
       </c>
-      <c r="T19">
+      <c r="U19">
+        <v>1.26</v>
+      </c>
+      <c r="V19">
+        <v>9</v>
+      </c>
+      <c r="W19">
+        <v>1.03</v>
+      </c>
+      <c r="X19">
+        <v>1.05</v>
+      </c>
+      <c r="Y19">
+        <v>6.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.44</v>
+      </c>
+      <c r="AA19">
+        <v>2.45</v>
+      </c>
+      <c r="AB19">
         <v>2.5</v>
       </c>
-      <c r="U19">
+      <c r="AC19">
         <v>1.5</v>
       </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.2</v>
-      </c>
-      <c r="AA19">
-        <v>4.33</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>2.1</v>
-      </c>
       <c r="AD19">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE19">
+        <v>1.11</v>
+      </c>
+      <c r="AF19">
+        <v>2.25</v>
+      </c>
+      <c r="AG19">
         <v>1.5</v>
       </c>
-      <c r="AF19">
-        <v>1.67</v>
-      </c>
-      <c r="AG19">
-        <v>2.1</v>
-      </c>
       <c r="AH19">
-        <v>4.25</v>
+        <v>11.5</v>
       </c>
       <c r="AI19">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M20">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N20">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
+        <v>1.3</v>
+      </c>
+      <c r="S20">
+        <v>3.4</v>
+      </c>
+      <c r="T20">
+        <v>2.5</v>
+      </c>
+      <c r="U20">
         <v>1.5</v>
       </c>
-      <c r="S20">
-        <v>2.4</v>
-      </c>
-      <c r="T20">
-        <v>3.4</v>
-      </c>
-      <c r="U20">
-        <v>1.25</v>
-      </c>
       <c r="V20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AA20">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB20">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
+        <v>2.1</v>
+      </c>
+      <c r="AD20">
+        <v>2.5</v>
+      </c>
+      <c r="AE20">
         <v>1.5</v>
       </c>
-      <c r="AD20">
-        <v>5</v>
-      </c>
-      <c r="AE20">
-        <v>1.16</v>
-      </c>
       <c r="AF20">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI20">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3553,13 +3553,13 @@
         <v>116</v>
       </c>
       <c r="L25">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="M25">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="N25">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="O25">
         <v>1.9</v>
@@ -3574,16 +3574,16 @@
         <v>1.52</v>
       </c>
       <c r="S25">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="T25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V25">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -3598,16 +3598,16 @@
         <v>1.5</v>
       </c>
       <c r="AA25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB25">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AC25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD25">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE25">
         <v>1.18</v>
@@ -3616,13 +3616,13 @@
         <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="s">
         <v>117</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -169,48 +169,48 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -229,39 +229,39 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
-    <t>Gnistan</t>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
@@ -274,12 +274,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Unión La Calera</t>
-  </si>
-  <si>
     <t>Tombense</t>
   </si>
   <si>
@@ -298,39 +298,39 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
+    <t>HJK</t>
+  </si>
+  <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
-  </si>
-  <si>
-    <t>HJK</t>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Trelleborg</t>
   </si>
   <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
+    <t>Honvéd W</t>
   </si>
   <si>
     <t>Primorje</t>
   </si>
   <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
@@ -343,10 +343,10 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
   </si>
   <si>
     <t>Maringá</t>
@@ -891,7 +891,7 @@
         <v>3.02</v>
       </c>
       <c r="N2">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="O2">
         <v>1.57</v>
@@ -903,52 +903,52 @@
         <v>2.9</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
         <v>2.54</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U2">
         <v>1.28</v>
       </c>
       <c r="V2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2">
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Z2">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AA2">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB2">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AC2">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD2">
         <v>4.2</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF2">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AG2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AH2">
         <v>8.5</v>
@@ -1001,76 +1001,76 @@
         <v>116</v>
       </c>
       <c r="L3">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M3">
+        <v>3.21</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3">
+        <v>1.66</v>
+      </c>
+      <c r="P3">
+        <v>7.5</v>
+      </c>
+      <c r="Q3">
+        <v>2.71</v>
+      </c>
+      <c r="R3">
+        <v>1.44</v>
+      </c>
+      <c r="S3">
+        <v>2.59</v>
+      </c>
+      <c r="T3">
+        <v>3.04</v>
+      </c>
+      <c r="U3">
+        <v>1.33</v>
+      </c>
+      <c r="V3">
+        <v>7.4</v>
+      </c>
+      <c r="W3">
+        <v>1.03</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>7.5</v>
+      </c>
+      <c r="Z3">
+        <v>1.33</v>
+      </c>
+      <c r="AA3">
         <v>2.84</v>
       </c>
-      <c r="N3">
-        <v>2.4</v>
-      </c>
-      <c r="O3">
-        <v>2.34</v>
-      </c>
-      <c r="P3">
-        <v>6.4</v>
-      </c>
-      <c r="Q3">
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>1.61</v>
+      </c>
+      <c r="AD3">
+        <v>3.6</v>
+      </c>
+      <c r="AE3">
+        <v>1.21</v>
+      </c>
+      <c r="AF3">
         <v>1.92</v>
       </c>
-      <c r="R3">
-        <v>1.45</v>
-      </c>
-      <c r="S3">
-        <v>2.45</v>
-      </c>
-      <c r="T3">
-        <v>3.3</v>
-      </c>
-      <c r="U3">
-        <v>1.28</v>
-      </c>
-      <c r="V3">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W3">
-        <v>1.02</v>
-      </c>
-      <c r="X3">
-        <v>1.06</v>
-      </c>
-      <c r="Y3">
-        <v>8</v>
-      </c>
-      <c r="Z3">
-        <v>1.46</v>
-      </c>
-      <c r="AA3">
-        <v>2.6</v>
-      </c>
-      <c r="AB3">
-        <v>2.25</v>
-      </c>
-      <c r="AC3">
-        <v>1.53</v>
-      </c>
-      <c r="AD3">
-        <v>4.33</v>
-      </c>
-      <c r="AE3">
-        <v>1.15</v>
-      </c>
-      <c r="AF3">
-        <v>2</v>
-      </c>
       <c r="AG3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI3">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
         <v>117</v>
@@ -1093,7 +1093,7 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>72</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P4">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q4">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V4">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA4">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AF4">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1209,7 +1209,7 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -1233,76 +1233,76 @@
         <v>116</v>
       </c>
       <c r="L5">
-        <v>3.85</v>
+        <v>2.71</v>
       </c>
       <c r="M5">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N5">
-        <v>1.68</v>
+        <v>2.33</v>
       </c>
       <c r="O5">
+        <v>2.34</v>
+      </c>
+      <c r="P5">
+        <v>6.4</v>
+      </c>
+      <c r="Q5">
+        <v>1.92</v>
+      </c>
+      <c r="R5">
+        <v>1.45</v>
+      </c>
+      <c r="S5">
         <v>2.4</v>
       </c>
-      <c r="P5">
-        <v>14</v>
-      </c>
-      <c r="Q5">
-        <v>1.57</v>
-      </c>
-      <c r="R5">
-        <v>1.25</v>
-      </c>
-      <c r="S5">
-        <v>3.3</v>
-      </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="V5">
-        <v>4.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W5">
+        <v>1.05</v>
+      </c>
+      <c r="X5">
+        <v>1.06</v>
+      </c>
+      <c r="Y5">
+        <v>6.25</v>
+      </c>
+      <c r="Z5">
+        <v>1.44</v>
+      </c>
+      <c r="AA5">
+        <v>2.55</v>
+      </c>
+      <c r="AB5">
+        <v>2.42</v>
+      </c>
+      <c r="AC5">
+        <v>1.53</v>
+      </c>
+      <c r="AD5">
+        <v>4.33</v>
+      </c>
+      <c r="AE5">
         <v>1.15</v>
       </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>12</v>
-      </c>
-      <c r="Z5">
-        <v>1.17</v>
-      </c>
-      <c r="AA5">
-        <v>4.97</v>
-      </c>
-      <c r="AB5">
-        <v>1.55</v>
-      </c>
-      <c r="AC5">
-        <v>2.29</v>
-      </c>
-      <c r="AD5">
-        <v>2.35</v>
-      </c>
-      <c r="AE5">
-        <v>1.52</v>
-      </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AH5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="s">
         <v>117</v>
@@ -1349,40 +1349,40 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="M6">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="O6">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P6">
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.05</v>
@@ -1391,34 +1391,34 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA6">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC6">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AD6">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AE6">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH6">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AI6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1465,76 +1465,76 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M7">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N7">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1557,7 +1557,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -1581,76 +1581,76 @@
         <v>116</v>
       </c>
       <c r="L8">
+        <v>1.63</v>
+      </c>
+      <c r="M8">
+        <v>3.64</v>
+      </c>
+      <c r="N8">
+        <v>4.33</v>
+      </c>
+      <c r="O8">
+        <v>1.57</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+      <c r="Q8">
+        <v>2.6</v>
+      </c>
+      <c r="R8">
+        <v>1.33</v>
+      </c>
+      <c r="S8">
         <v>3.25</v>
       </c>
-      <c r="M8">
-        <v>3.15</v>
-      </c>
-      <c r="N8">
-        <v>2.12</v>
-      </c>
-      <c r="O8">
-        <v>2.3</v>
-      </c>
-      <c r="P8">
-        <v>9</v>
-      </c>
-      <c r="Q8">
-        <v>1.8</v>
-      </c>
-      <c r="R8">
-        <v>1.45</v>
-      </c>
-      <c r="S8">
-        <v>2.69</v>
-      </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U8">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
         <v>6.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA8">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>1.94</v>
+      </c>
+      <c r="AD8">
+        <v>3.1</v>
+      </c>
+      <c r="AE8">
+        <v>1.38</v>
+      </c>
+      <c r="AF8">
+        <v>1.8</v>
+      </c>
+      <c r="AG8">
         <v>1.95</v>
       </c>
-      <c r="AC8">
-        <v>1.73</v>
-      </c>
-      <c r="AD8">
-        <v>3.34</v>
-      </c>
-      <c r="AE8">
-        <v>1.25</v>
-      </c>
-      <c r="AF8">
-        <v>1.78</v>
-      </c>
-      <c r="AG8">
-        <v>1.91</v>
-      </c>
       <c r="AH8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,16 +1670,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1697,13 +1697,13 @@
         <v>116</v>
       </c>
       <c r="L9">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N9">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>1.8</v>
@@ -1715,19 +1715,19 @@
         <v>2.1</v>
       </c>
       <c r="R9">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W9">
         <v>1.06</v>
@@ -1736,25 +1736,25 @@
         <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AA9">
         <v>3.75</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF9">
         <v>1.62</v>
@@ -1763,10 +1763,10 @@
         <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>5.3</v>
+        <v>5.47</v>
       </c>
       <c r="AI9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="s">
         <v>117</v>
@@ -1786,16 +1786,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1813,76 +1813,76 @@
         <v>116</v>
       </c>
       <c r="L10">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="M10">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N10">
-        <v>3.11</v>
+        <v>2.55</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R10">
+        <v>1.38</v>
+      </c>
+      <c r="S10">
+        <v>2.8</v>
+      </c>
+      <c r="T10">
+        <v>2.75</v>
+      </c>
+      <c r="U10">
+        <v>1.4</v>
+      </c>
+      <c r="V10">
+        <v>7.5</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.06</v>
+      </c>
+      <c r="Y10">
+        <v>9</v>
+      </c>
+      <c r="Z10">
         <v>1.3</v>
       </c>
-      <c r="S10">
+      <c r="AA10">
+        <v>3.45</v>
+      </c>
+      <c r="AB10">
+        <v>1.92</v>
+      </c>
+      <c r="AC10">
+        <v>1.78</v>
+      </c>
+      <c r="AD10">
         <v>3.4</v>
       </c>
-      <c r="T10">
-        <v>2.5</v>
-      </c>
-      <c r="U10">
-        <v>1.5</v>
-      </c>
-      <c r="V10">
-        <v>6</v>
-      </c>
-      <c r="W10">
-        <v>1.13</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>10</v>
-      </c>
-      <c r="Z10">
-        <v>1.22</v>
-      </c>
-      <c r="AA10">
-        <v>4.2</v>
-      </c>
-      <c r="AB10">
-        <v>1.69</v>
-      </c>
-      <c r="AC10">
-        <v>2.04</v>
-      </c>
-      <c r="AD10">
-        <v>2.7</v>
-      </c>
       <c r="AE10">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI10">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="s">
         <v>117</v>
@@ -1902,16 +1902,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,37 +1929,37 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N11">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P11">
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
         <v>1.38</v>
       </c>
       <c r="S11">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>1.08</v>
@@ -1974,31 +1974,31 @@
         <v>1.3</v>
       </c>
       <c r="AA11">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AB11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC11">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE11">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH11">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,16 +2018,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="M12">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>5.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AC12">
-        <v>1.91</v>
+        <v>2.74</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2161,22 +2161,22 @@
         <v>116</v>
       </c>
       <c r="L13">
-        <v>1.52</v>
+        <v>2.36</v>
       </c>
       <c r="M13">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>2.85</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2277,64 +2277,64 @@
         <v>116</v>
       </c>
       <c r="L14">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N14">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>1.67</v>
+      </c>
+      <c r="AC14">
         <v>2.1</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>1.9</v>
-      </c>
-      <c r="AC14">
-        <v>1.9</v>
-      </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>68</v>
@@ -2393,13 +2393,13 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="M15">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N15">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="O15">
         <v>2.5</v>
@@ -2411,58 +2411,58 @@
         <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
         <v>1.3</v>
       </c>
       <c r="V15">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Z15">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AA15">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AC15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD15">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
         <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2509,13 +2509,13 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="M16">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="N16">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="O16">
         <v>1.22</v>
@@ -2557,10 +2557,10 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AC16">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AD16">
         <v>1.6</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2741,13 +2741,13 @@
         <v>116</v>
       </c>
       <c r="L18">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N18">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
         <v>1.55</v>
@@ -2759,16 +2759,16 @@
         <v>2.42</v>
       </c>
       <c r="R18">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U18">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V18">
         <v>4.33</v>
@@ -2780,7 +2780,7 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z18">
         <v>1.1</v>
@@ -2789,25 +2789,25 @@
         <v>5.25</v>
       </c>
       <c r="AB18">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AC18">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AD18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE18">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AH18">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AI18">
         <v>1.29</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>1.65</v>
+        <v>5.25</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N19">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P19">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R19">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="T19">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AA19">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="AB19">
+        <v>1.7</v>
+      </c>
+      <c r="AC19">
+        <v>2.1</v>
+      </c>
+      <c r="AD19">
         <v>2.5</v>
       </c>
-      <c r="AC19">
+      <c r="AE19">
         <v>1.5</v>
       </c>
-      <c r="AD19">
-        <v>5</v>
-      </c>
-      <c r="AE19">
-        <v>1.11</v>
-      </c>
       <c r="AF19">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH19">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI19">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>5.25</v>
+        <v>1.73</v>
       </c>
       <c r="M20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="O20">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S20">
+        <v>2.3</v>
+      </c>
+      <c r="T20">
         <v>3.4</v>
       </c>
-      <c r="T20">
-        <v>2.5</v>
-      </c>
       <c r="U20">
+        <v>1.25</v>
+      </c>
+      <c r="V20">
+        <v>9</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.09</v>
+      </c>
+      <c r="Y20">
+        <v>6.65</v>
+      </c>
+      <c r="Z20">
+        <v>1.44</v>
+      </c>
+      <c r="AA20">
+        <v>2.43</v>
+      </c>
+      <c r="AB20">
+        <v>2.4</v>
+      </c>
+      <c r="AC20">
+        <v>1.47</v>
+      </c>
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>1.16</v>
+      </c>
+      <c r="AF20">
+        <v>2.25</v>
+      </c>
+      <c r="AG20">
         <v>1.5</v>
       </c>
-      <c r="V20">
-        <v>6</v>
-      </c>
-      <c r="W20">
-        <v>1.13</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>9.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.2</v>
-      </c>
-      <c r="AA20">
-        <v>4.33</v>
-      </c>
-      <c r="AB20">
-        <v>1.7</v>
-      </c>
-      <c r="AC20">
-        <v>2.1</v>
-      </c>
-      <c r="AD20">
-        <v>2.5</v>
-      </c>
-      <c r="AE20">
-        <v>1.5</v>
-      </c>
-      <c r="AF20">
-        <v>1.67</v>
-      </c>
-      <c r="AG20">
-        <v>2.1</v>
-      </c>
       <c r="AH20">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="AI20">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3110,13 +3110,13 @@
         <v>1.51</v>
       </c>
       <c r="S21">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T21">
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -3125,10 +3125,10 @@
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z21">
         <v>1.48</v>
@@ -3155,10 +3155,10 @@
         <v>1.7</v>
       </c>
       <c r="AH21">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AI21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="s">
         <v>117</v>
@@ -3226,10 +3226,10 @@
         <v>1.6</v>
       </c>
       <c r="S22">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="T22">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
         <v>1.22</v>
@@ -3238,13 +3238,13 @@
         <v>11</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y22">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Z22">
         <v>1.53</v>
@@ -3262,7 +3262,7 @@
         <v>5.5</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
         <v>2.35</v>
@@ -3271,7 +3271,7 @@
         <v>1.5</v>
       </c>
       <c r="AH22">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI22">
         <v>1.01</v>
@@ -3327,7 +3327,7 @@
         <v>3.5</v>
       </c>
       <c r="N23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>1.73</v>
@@ -3345,52 +3345,52 @@
         <v>2.06</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="U23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V23">
         <v>11</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y23">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Z23">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AA23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB23">
         <v>3.4</v>
       </c>
       <c r="AC23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD23">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AG23">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AH23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="s">
         <v>117</v>
@@ -3437,13 +3437,13 @@
         <v>116</v>
       </c>
       <c r="L24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M24">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="N24">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O24">
         <v>1.8</v>
@@ -3455,43 +3455,43 @@
         <v>2.3</v>
       </c>
       <c r="R24">
+        <v>1.4</v>
+      </c>
+      <c r="S24">
+        <v>2.7</v>
+      </c>
+      <c r="T24">
+        <v>2.9</v>
+      </c>
+      <c r="U24">
         <v>1.36</v>
       </c>
-      <c r="S24">
-        <v>2.78</v>
-      </c>
-      <c r="T24">
-        <v>2.8</v>
-      </c>
-      <c r="U24">
-        <v>1.38</v>
-      </c>
       <c r="V24">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z24">
         <v>1.35</v>
       </c>
       <c r="AA24">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AD24">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AE24">
         <v>1.29</v>
@@ -3500,13 +3500,13 @@
         <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH24">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AI24">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ24" t="s">
         <v>117</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3553,7 +3553,7 @@
         <v>116</v>
       </c>
       <c r="L25">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="M25">
         <v>2.8</v>
@@ -3571,34 +3571,34 @@
         <v>2.4</v>
       </c>
       <c r="R25">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S25">
         <v>2.5</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U25">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="Z25">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA25">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AB25">
         <v>2.44</v>
@@ -3607,16 +3607,16 @@
         <v>1.53</v>
       </c>
       <c r="AD25">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG25">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH25">
         <v>10</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -178,21 +178,21 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
@@ -238,36 +238,36 @@
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
+    <t>Odra Opole</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
     <t>Videoton</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
+    <t>B36</t>
+  </si>
+  <si>
     <t>Montana</t>
   </si>
   <si>
-    <t>B36</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Avaí</t>
   </si>
   <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
     <t>Tombense</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
@@ -307,36 +307,36 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Trelleborg</t>
+    <t>Miedź Legnica</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
     <t>Primorje</t>
   </si>
   <si>
+    <t>TB</t>
+  </si>
+  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>TB</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -349,10 +349,10 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Maringá</t>
-  </si>
-  <si>
-    <t>Brusque</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
@@ -1349,40 +1349,40 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M6">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N6">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O6">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P6">
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.05</v>
@@ -1391,34 +1391,34 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA6">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB6">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD6">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE6">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH6">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1557,7 +1557,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -1581,76 +1581,76 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="M8">
-        <v>3.64</v>
+        <v>4.4</v>
       </c>
       <c r="N8">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
       <c r="O8">
+        <v>1.4</v>
+      </c>
+      <c r="P8">
+        <v>17</v>
+      </c>
+      <c r="Q8">
+        <v>2.75</v>
+      </c>
+      <c r="R8">
+        <v>1.22</v>
+      </c>
+      <c r="S8">
+        <v>3.8</v>
+      </c>
+      <c r="T8">
+        <v>2.03</v>
+      </c>
+      <c r="U8">
+        <v>1.7</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>1.18</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>16</v>
+      </c>
+      <c r="Z8">
+        <v>1.07</v>
+      </c>
+      <c r="AA8">
+        <v>5.36</v>
+      </c>
+      <c r="AB8">
+        <v>1.4</v>
+      </c>
+      <c r="AC8">
+        <v>2.74</v>
+      </c>
+      <c r="AD8">
+        <v>2.05</v>
+      </c>
+      <c r="AE8">
+        <v>1.72</v>
+      </c>
+      <c r="AF8">
         <v>1.57</v>
       </c>
-      <c r="P8">
-        <v>10</v>
-      </c>
-      <c r="Q8">
-        <v>2.6</v>
-      </c>
-      <c r="R8">
-        <v>1.33</v>
-      </c>
-      <c r="S8">
-        <v>3.25</v>
-      </c>
-      <c r="T8">
-        <v>2.63</v>
-      </c>
-      <c r="U8">
-        <v>1.44</v>
-      </c>
-      <c r="V8">
-        <v>6.5</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.05</v>
-      </c>
-      <c r="Y8">
-        <v>10</v>
-      </c>
-      <c r="Z8">
+      <c r="AG8">
+        <v>2.25</v>
+      </c>
+      <c r="AH8">
+        <v>3.3</v>
+      </c>
+      <c r="AI8">
         <v>1.28</v>
-      </c>
-      <c r="AA8">
-        <v>3.8</v>
-      </c>
-      <c r="AB8">
-        <v>1.76</v>
-      </c>
-      <c r="AC8">
-        <v>1.94</v>
-      </c>
-      <c r="AD8">
-        <v>3.1</v>
-      </c>
-      <c r="AE8">
-        <v>1.38</v>
-      </c>
-      <c r="AF8">
-        <v>1.8</v>
-      </c>
-      <c r="AG8">
-        <v>1.95</v>
-      </c>
-      <c r="AH8">
-        <v>5.75</v>
-      </c>
-      <c r="AI8">
-        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1786,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
@@ -1813,76 +1813,76 @@
         <v>116</v>
       </c>
       <c r="L10">
-        <v>2.65</v>
+        <v>1.96</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N10">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA10">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB10">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AC10">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AD10">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI10">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="s">
         <v>117</v>
@@ -1902,7 +1902,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>68</v>
@@ -2018,10 +2018,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="M12">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>2.55</v>
       </c>
       <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>9</v>
+      </c>
+      <c r="Q12">
+        <v>2.05</v>
+      </c>
+      <c r="R12">
+        <v>1.38</v>
+      </c>
+      <c r="S12">
+        <v>2.8</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
         <v>1.4</v>
       </c>
-      <c r="P12">
-        <v>17</v>
-      </c>
-      <c r="Q12">
-        <v>2.75</v>
-      </c>
-      <c r="R12">
-        <v>1.22</v>
-      </c>
-      <c r="S12">
-        <v>3.8</v>
-      </c>
-      <c r="T12">
-        <v>2.03</v>
-      </c>
-      <c r="U12">
-        <v>1.7</v>
-      </c>
       <c r="V12">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AA12">
-        <v>5.36</v>
+        <v>3.45</v>
       </c>
       <c r="AB12">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="AD12">
+        <v>3.4</v>
+      </c>
+      <c r="AE12">
+        <v>1.33</v>
+      </c>
+      <c r="AF12">
+        <v>1.67</v>
+      </c>
+      <c r="AG12">
         <v>2.05</v>
       </c>
-      <c r="AE12">
-        <v>1.72</v>
-      </c>
-      <c r="AF12">
-        <v>1.57</v>
-      </c>
-      <c r="AG12">
-        <v>2.25</v>
-      </c>
       <c r="AH12">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AI12">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2366,10 +2366,10 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
@@ -2393,76 +2393,76 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="M15">
+        <v>7.68</v>
+      </c>
+      <c r="N15">
+        <v>12</v>
+      </c>
+      <c r="O15">
+        <v>1.22</v>
+      </c>
+      <c r="P15">
+        <v>26</v>
+      </c>
+      <c r="Q15">
+        <v>4.2</v>
+      </c>
+      <c r="R15">
+        <v>1.13</v>
+      </c>
+      <c r="S15">
+        <v>5</v>
+      </c>
+      <c r="T15">
+        <v>1.65</v>
+      </c>
+      <c r="U15">
+        <v>2.05</v>
+      </c>
+      <c r="V15">
         <v>3.2</v>
       </c>
-      <c r="N15">
-        <v>1.94</v>
-      </c>
-      <c r="O15">
-        <v>2.5</v>
-      </c>
-      <c r="P15">
-        <v>7.1</v>
-      </c>
-      <c r="Q15">
+      <c r="W15">
+        <v>1.3</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>41</v>
+      </c>
+      <c r="Z15">
+        <v>1.03</v>
+      </c>
+      <c r="AA15">
+        <v>7.5</v>
+      </c>
+      <c r="AB15">
+        <v>1.25</v>
+      </c>
+      <c r="AC15">
+        <v>3.75</v>
+      </c>
+      <c r="AD15">
+        <v>1.6</v>
+      </c>
+      <c r="AE15">
+        <v>2.14</v>
+      </c>
+      <c r="AF15">
         <v>1.73</v>
       </c>
-      <c r="R15">
-        <v>1.44</v>
-      </c>
-      <c r="S15">
-        <v>2.45</v>
-      </c>
-      <c r="T15">
-        <v>3.2</v>
-      </c>
-      <c r="U15">
-        <v>1.3</v>
-      </c>
-      <c r="V15">
-        <v>9</v>
-      </c>
-      <c r="W15">
-        <v>1.04</v>
-      </c>
-      <c r="X15">
-        <v>1.08</v>
-      </c>
-      <c r="Y15">
-        <v>7.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.38</v>
-      </c>
-      <c r="AA15">
-        <v>2.63</v>
-      </c>
-      <c r="AB15">
-        <v>2.32</v>
-      </c>
-      <c r="AC15">
-        <v>1.57</v>
-      </c>
-      <c r="AD15">
-        <v>4.27</v>
-      </c>
-      <c r="AE15">
-        <v>1.18</v>
-      </c>
-      <c r="AF15">
-        <v>1.95</v>
-      </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>9.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI15">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2482,10 +2482,10 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
@@ -2509,76 +2509,76 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>1.14</v>
+        <v>3.8</v>
       </c>
       <c r="M16">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="N16">
-        <v>11</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="P16">
-        <v>26</v>
+        <v>7.1</v>
       </c>
       <c r="Q16">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="T16">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="V16">
-        <v>3.28</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="Z16">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>2.63</v>
       </c>
       <c r="AB16">
-        <v>1.23</v>
+        <v>2.32</v>
       </c>
       <c r="AC16">
-        <v>3.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD16">
-        <v>1.6</v>
+        <v>4.27</v>
       </c>
       <c r="AE16">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AH16">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="AI16">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AJ16" t="s">
         <v>117</v>
@@ -3089,43 +3089,43 @@
         <v>116</v>
       </c>
       <c r="L21">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="M21">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N21">
-        <v>2.67</v>
+        <v>4.45</v>
       </c>
       <c r="O21">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P21">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q21">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S21">
         <v>2.4</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
         <v>6.5</v>
@@ -3134,31 +3134,31 @@
         <v>1.48</v>
       </c>
       <c r="AA21">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC21">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD21">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AE21">
         <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG21">
         <v>1.7</v>
       </c>
       <c r="AH21">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ21" t="s">
         <v>117</v>
@@ -3205,76 +3205,76 @@
         <v>116</v>
       </c>
       <c r="L22">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M22">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P22">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q22">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R22">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="S22">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="T22">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z22">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA22">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB22">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="AC22">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AD22">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ22" t="s">
         <v>117</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -169,30 +169,30 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -229,30 +229,30 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Västerås SK</t>
   </si>
   <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
     <t>Helsingborg</t>
   </si>
   <si>
@@ -274,12 +274,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
@@ -298,30 +298,30 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
     <t>HJK</t>
   </si>
   <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
     <t>Trelleborg</t>
   </si>
   <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
@@ -343,10 +343,10 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
   </si>
   <si>
     <t>Brusque</t>
@@ -1001,76 +1001,76 @@
         <v>116</v>
       </c>
       <c r="L3">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M3">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="P3">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q3">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
+        <v>1.45</v>
+      </c>
+      <c r="S3">
+        <v>2.4</v>
+      </c>
+      <c r="T3">
+        <v>3.2</v>
+      </c>
+      <c r="U3">
+        <v>1.29</v>
+      </c>
+      <c r="V3">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W3">
+        <v>1.05</v>
+      </c>
+      <c r="X3">
+        <v>1.06</v>
+      </c>
+      <c r="Y3">
+        <v>6.25</v>
+      </c>
+      <c r="Z3">
         <v>1.44</v>
       </c>
-      <c r="S3">
-        <v>2.59</v>
-      </c>
-      <c r="T3">
-        <v>3.04</v>
-      </c>
-      <c r="U3">
-        <v>1.33</v>
-      </c>
-      <c r="V3">
-        <v>7.4</v>
-      </c>
-      <c r="W3">
-        <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>7.5</v>
-      </c>
-      <c r="Z3">
-        <v>1.33</v>
-      </c>
       <c r="AA3">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD3">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AE3">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="s">
         <v>117</v>
@@ -1093,7 +1093,7 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>72</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>4.1</v>
+        <v>1.79</v>
       </c>
       <c r="M4">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q4">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="AB4">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AD4">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE4">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AG4">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI4">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1209,7 +1209,7 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -1233,76 +1233,76 @@
         <v>116</v>
       </c>
       <c r="L5">
-        <v>2.71</v>
+        <v>4.1</v>
       </c>
       <c r="M5">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N5">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="O5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="P5">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U5">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>8.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="AB5">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>1.76</v>
+        <v>2.21</v>
       </c>
       <c r="AH5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AI5">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AJ5" t="s">
         <v>117</v>
@@ -1465,76 +1465,76 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N7">
-        <v>2.99</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB7">
+        <v>1.93</v>
+      </c>
+      <c r="AC7">
         <v>1.73</v>
       </c>
-      <c r="AC7">
-        <v>1.91</v>
-      </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1581,76 +1581,76 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N8">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="W8">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AA8">
-        <v>5.36</v>
+        <v>3.75</v>
       </c>
       <c r="AB8">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="AD8">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AE8">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH8">
-        <v>3.3</v>
+        <v>5.47</v>
       </c>
       <c r="AI8">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,16 +1670,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1697,76 +1697,76 @@
         <v>116</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O9">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD9">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
         <v>117</v>
@@ -1929,76 +1929,76 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M11">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N11">
+        <v>5.3</v>
+      </c>
+      <c r="O11">
+        <v>1.4</v>
+      </c>
+      <c r="P11">
+        <v>17</v>
+      </c>
+      <c r="Q11">
+        <v>2.75</v>
+      </c>
+      <c r="R11">
+        <v>1.22</v>
+      </c>
+      <c r="S11">
+        <v>3.8</v>
+      </c>
+      <c r="T11">
+        <v>2.03</v>
+      </c>
+      <c r="U11">
+        <v>1.7</v>
+      </c>
+      <c r="V11">
+        <v>4</v>
+      </c>
+      <c r="W11">
+        <v>1.18</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>16</v>
+      </c>
+      <c r="Z11">
+        <v>1.07</v>
+      </c>
+      <c r="AA11">
+        <v>5.36</v>
+      </c>
+      <c r="AB11">
+        <v>1.4</v>
+      </c>
+      <c r="AC11">
+        <v>2.74</v>
+      </c>
+      <c r="AD11">
         <v>2.05</v>
       </c>
-      <c r="O11">
-        <v>2.3</v>
-      </c>
-      <c r="P11">
-        <v>9</v>
-      </c>
-      <c r="Q11">
-        <v>1.8</v>
-      </c>
-      <c r="R11">
-        <v>1.38</v>
-      </c>
-      <c r="S11">
-        <v>2.78</v>
-      </c>
-      <c r="T11">
-        <v>3.14</v>
-      </c>
-      <c r="U11">
-        <v>1.33</v>
-      </c>
-      <c r="V11">
-        <v>8</v>
-      </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.06</v>
-      </c>
-      <c r="Y11">
-        <v>9</v>
-      </c>
-      <c r="Z11">
-        <v>1.3</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
-      </c>
-      <c r="AB11">
-        <v>1.93</v>
-      </c>
-      <c r="AC11">
-        <v>1.73</v>
-      </c>
-      <c r="AD11">
-        <v>3.5</v>
-      </c>
       <c r="AE11">
+        <v>1.72</v>
+      </c>
+      <c r="AF11">
+        <v>1.57</v>
+      </c>
+      <c r="AG11">
+        <v>2.25</v>
+      </c>
+      <c r="AH11">
+        <v>3.3</v>
+      </c>
+      <c r="AI11">
         <v>1.28</v>
-      </c>
-      <c r="AF11">
-        <v>1.81</v>
-      </c>
-      <c r="AG11">
-        <v>1.88</v>
-      </c>
-      <c r="AH11">
-        <v>7</v>
-      </c>
-      <c r="AI11">
-        <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2482,7 +2482,7 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>68</v>
@@ -2509,13 +2509,13 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="M16">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -2557,10 +2557,10 @@
         <v>2.63</v>
       </c>
       <c r="AB16">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD16">
         <v>4.27</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2741,13 +2741,13 @@
         <v>116</v>
       </c>
       <c r="L18">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M18">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
         <v>1.55</v>
@@ -2759,19 +2759,19 @@
         <v>2.42</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S18">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T18">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V18">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="W18">
         <v>1.18</v>
@@ -2786,19 +2786,19 @@
         <v>1.1</v>
       </c>
       <c r="AA18">
-        <v>5.25</v>
+        <v>5.61</v>
       </c>
       <c r="AB18">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC18">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AD18">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AE18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF18">
         <v>1.45</v>
@@ -2807,10 +2807,10 @@
         <v>2.5</v>
       </c>
       <c r="AH18">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AI18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AJ18" t="s">
         <v>117</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>5.25</v>
+        <v>1.75</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>4.25</v>
       </c>
       <c r="O19">
+        <v>1.58</v>
+      </c>
+      <c r="P19">
+        <v>6.5</v>
+      </c>
+      <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="R19">
+        <v>1.5</v>
+      </c>
+      <c r="S19">
+        <v>2.5</v>
+      </c>
+      <c r="T19">
+        <v>3.56</v>
+      </c>
+      <c r="U19">
+        <v>1.29</v>
+      </c>
+      <c r="V19">
+        <v>9</v>
+      </c>
+      <c r="W19">
+        <v>1.03</v>
+      </c>
+      <c r="X19">
+        <v>1.1</v>
+      </c>
+      <c r="Y19">
+        <v>6.95</v>
+      </c>
+      <c r="Z19">
+        <v>1.51</v>
+      </c>
+      <c r="AA19">
+        <v>2.4</v>
+      </c>
+      <c r="AB19">
         <v>2.6</v>
       </c>
-      <c r="P19">
-        <v>12.5</v>
-      </c>
-      <c r="Q19">
-        <v>1.53</v>
-      </c>
-      <c r="R19">
-        <v>1.3</v>
-      </c>
-      <c r="S19">
-        <v>3.4</v>
-      </c>
-      <c r="T19">
-        <v>2.5</v>
-      </c>
-      <c r="U19">
-        <v>1.5</v>
-      </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.2</v>
-      </c>
-      <c r="AA19">
-        <v>4.33</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
       <c r="AC19">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AD19">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="AE19">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH19">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="AI19">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>1.73</v>
+        <v>5.25</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N20">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>6.65</v>
+        <v>9.5</v>
       </c>
       <c r="Z20">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AA20">
-        <v>2.43</v>
+        <v>4.33</v>
       </c>
       <c r="AB20">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AF20">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>10.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI20">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3089,13 +3089,13 @@
         <v>116</v>
       </c>
       <c r="L21">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M21">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N21">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
         <v>1.67</v>
@@ -3107,10 +3107,10 @@
         <v>2.82</v>
       </c>
       <c r="R21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T21">
         <v>3.5</v>
@@ -3125,22 +3125,22 @@
         <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="Z21">
         <v>1.48</v>
       </c>
       <c r="AA21">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AB21">
         <v>2.75</v>
       </c>
       <c r="AC21">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD21">
         <v>4.75</v>
@@ -3152,13 +3152,13 @@
         <v>1.97</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH21">
         <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ21" t="s">
         <v>117</v>
@@ -3208,10 +3208,10 @@
         <v>2.45</v>
       </c>
       <c r="M22">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
         <v>2.15</v>
@@ -3226,19 +3226,19 @@
         <v>1.51</v>
       </c>
       <c r="S22">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T22">
         <v>3.4</v>
       </c>
       <c r="U22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V22">
         <v>8</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.05</v>
@@ -3250,31 +3250,31 @@
         <v>1.48</v>
       </c>
       <c r="AA22">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB22">
         <v>2.42</v>
       </c>
       <c r="AC22">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AD22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AE22">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
         <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH22">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AI22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="s">
         <v>117</v>
@@ -3321,13 +3321,13 @@
         <v>116</v>
       </c>
       <c r="L23">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="M23">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="O23">
         <v>1.73</v>
@@ -3360,25 +3360,25 @@
         <v>1.13</v>
       </c>
       <c r="Y23">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z23">
         <v>1.62</v>
       </c>
       <c r="AA23">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB23">
         <v>3.4</v>
       </c>
       <c r="AC23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD23">
         <v>6.41</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
         <v>2.5</v>
@@ -3437,13 +3437,13 @@
         <v>116</v>
       </c>
       <c r="L24">
-        <v>1.66</v>
+        <v>2.41</v>
       </c>
       <c r="M24">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="N24">
-        <v>5.1</v>
+        <v>2.61</v>
       </c>
       <c r="O24">
         <v>1.8</v>
@@ -3458,13 +3458,13 @@
         <v>1.4</v>
       </c>
       <c r="S24">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T24">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="U24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -3482,7 +3482,7 @@
         <v>1.35</v>
       </c>
       <c r="AA24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB24">
         <v>1.95</v>
@@ -3491,16 +3491,16 @@
         <v>1.8</v>
       </c>
       <c r="AD24">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AE24">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH24">
         <v>6.5</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3553,7 +3553,7 @@
         <v>116</v>
       </c>
       <c r="L25">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="M25">
         <v>2.8</v>
@@ -3574,28 +3574,28 @@
         <v>1.5</v>
       </c>
       <c r="S25">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="T25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z25">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA25">
         <v>2.53</v>
@@ -3607,10 +3607,10 @@
         <v>1.53</v>
       </c>
       <c r="AD25">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
         <v>2.2</v>
@@ -3619,10 +3619,10 @@
         <v>1.65</v>
       </c>
       <c r="AH25">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI25">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ25" t="s">
         <v>117</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -181,18 +181,18 @@
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -238,24 +238,24 @@
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
     <t>Västerås SK</t>
   </si>
   <si>
     <t>Odra Opole</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Videoton</t>
   </si>
   <si>
@@ -274,12 +274,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Unión La Calera</t>
-  </si>
-  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
@@ -307,24 +307,24 @@
     <t>HJK</t>
   </si>
   <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
     <t>Trelleborg</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
@@ -343,10 +343,10 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
   </si>
   <si>
     <t>Brusque</t>
@@ -1349,76 +1349,76 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="M6">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="O6">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
+        <v>1.38</v>
+      </c>
+      <c r="S6">
+        <v>2.8</v>
+      </c>
+      <c r="T6">
+        <v>2.75</v>
+      </c>
+      <c r="U6">
+        <v>1.4</v>
+      </c>
+      <c r="V6">
+        <v>7.5</v>
+      </c>
+      <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1.06</v>
+      </c>
+      <c r="Y6">
+        <v>9</v>
+      </c>
+      <c r="Z6">
+        <v>1.3</v>
+      </c>
+      <c r="AA6">
+        <v>3.45</v>
+      </c>
+      <c r="AB6">
+        <v>1.92</v>
+      </c>
+      <c r="AC6">
+        <v>1.78</v>
+      </c>
+      <c r="AD6">
+        <v>3.4</v>
+      </c>
+      <c r="AE6">
         <v>1.33</v>
       </c>
-      <c r="S6">
-        <v>3.25</v>
-      </c>
-      <c r="T6">
-        <v>2.63</v>
-      </c>
-      <c r="U6">
-        <v>1.44</v>
-      </c>
-      <c r="V6">
+      <c r="AF6">
+        <v>1.67</v>
+      </c>
+      <c r="AG6">
+        <v>2.05</v>
+      </c>
+      <c r="AH6">
         <v>6.5</v>
       </c>
-      <c r="W6">
+      <c r="AI6">
         <v>1.11</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>10</v>
-      </c>
-      <c r="Z6">
-        <v>1.28</v>
-      </c>
-      <c r="AA6">
-        <v>3.8</v>
-      </c>
-      <c r="AB6">
-        <v>1.76</v>
-      </c>
-      <c r="AC6">
-        <v>1.94</v>
-      </c>
-      <c r="AD6">
-        <v>3.1</v>
-      </c>
-      <c r="AE6">
-        <v>1.38</v>
-      </c>
-      <c r="AF6">
-        <v>1.8</v>
-      </c>
-      <c r="AG6">
-        <v>1.95</v>
-      </c>
-      <c r="AH6">
-        <v>5.75</v>
-      </c>
-      <c r="AI6">
-        <v>1.14</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1465,76 +1465,76 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M7">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N7">
+        <v>5.3</v>
+      </c>
+      <c r="O7">
+        <v>1.4</v>
+      </c>
+      <c r="P7">
+        <v>17</v>
+      </c>
+      <c r="Q7">
+        <v>2.75</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>3.8</v>
+      </c>
+      <c r="T7">
+        <v>2.03</v>
+      </c>
+      <c r="U7">
+        <v>1.7</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
+      </c>
+      <c r="W7">
+        <v>1.18</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>16</v>
+      </c>
+      <c r="Z7">
+        <v>1.07</v>
+      </c>
+      <c r="AA7">
+        <v>5.36</v>
+      </c>
+      <c r="AB7">
+        <v>1.4</v>
+      </c>
+      <c r="AC7">
+        <v>2.74</v>
+      </c>
+      <c r="AD7">
         <v>2.05</v>
       </c>
-      <c r="O7">
-        <v>2.3</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>1.8</v>
-      </c>
-      <c r="R7">
-        <v>1.38</v>
-      </c>
-      <c r="S7">
-        <v>2.78</v>
-      </c>
-      <c r="T7">
-        <v>3.14</v>
-      </c>
-      <c r="U7">
-        <v>1.33</v>
-      </c>
-      <c r="V7">
-        <v>8</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.06</v>
-      </c>
-      <c r="Y7">
-        <v>9</v>
-      </c>
-      <c r="Z7">
-        <v>1.3</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>1.93</v>
-      </c>
-      <c r="AC7">
-        <v>1.73</v>
-      </c>
-      <c r="AD7">
-        <v>3.5</v>
-      </c>
       <c r="AE7">
+        <v>1.72</v>
+      </c>
+      <c r="AF7">
+        <v>1.57</v>
+      </c>
+      <c r="AG7">
+        <v>2.25</v>
+      </c>
+      <c r="AH7">
+        <v>3.3</v>
+      </c>
+      <c r="AI7">
         <v>1.28</v>
-      </c>
-      <c r="AF7">
-        <v>1.81</v>
-      </c>
-      <c r="AG7">
-        <v>1.88</v>
-      </c>
-      <c r="AH7">
-        <v>7</v>
-      </c>
-      <c r="AI7">
-        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1557,7 +1557,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -1581,64 +1581,64 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="M8">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="O8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
         <v>2.5</v>
       </c>
       <c r="U8">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA8">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC8">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD8">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE8">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF8">
         <v>1.62</v>
@@ -1647,10 +1647,10 @@
         <v>2.2</v>
       </c>
       <c r="AH8">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="AI8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,16 +1670,16 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1786,16 +1786,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1813,40 +1813,40 @@
         <v>116</v>
       </c>
       <c r="L10">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M10">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N10">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P10">
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.05</v>
@@ -1855,34 +1855,34 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB10">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE10">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>117</v>
@@ -1902,16 +1902,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,76 +1929,76 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T11">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V11">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="W11">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z11">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AA11">
-        <v>5.36</v>
+        <v>3.75</v>
       </c>
       <c r="AB11">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="AD11">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AE11">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH11">
-        <v>3.3</v>
+        <v>5.47</v>
       </c>
       <c r="AI11">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,10 +2018,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
@@ -2045,37 +2045,37 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N12">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P12">
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
         <v>1.38</v>
       </c>
       <c r="S12">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V12">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2090,31 +2090,31 @@
         <v>1.3</v>
       </c>
       <c r="AA12">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE12">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH12">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>1.75</v>
+        <v>5.25</v>
       </c>
       <c r="M19">
+        <v>3.5</v>
+      </c>
+      <c r="N19">
+        <v>1.67</v>
+      </c>
+      <c r="O19">
+        <v>2.6</v>
+      </c>
+      <c r="P19">
+        <v>12.5</v>
+      </c>
+      <c r="Q19">
+        <v>1.53</v>
+      </c>
+      <c r="R19">
+        <v>1.3</v>
+      </c>
+      <c r="S19">
         <v>3.4</v>
       </c>
-      <c r="N19">
+      <c r="T19">
+        <v>2.5</v>
+      </c>
+      <c r="U19">
+        <v>1.5</v>
+      </c>
+      <c r="V19">
+        <v>6</v>
+      </c>
+      <c r="W19">
+        <v>1.13</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>9.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.2</v>
+      </c>
+      <c r="AA19">
+        <v>4.33</v>
+      </c>
+      <c r="AB19">
+        <v>1.7</v>
+      </c>
+      <c r="AC19">
+        <v>2.1</v>
+      </c>
+      <c r="AD19">
+        <v>2.5</v>
+      </c>
+      <c r="AE19">
+        <v>1.5</v>
+      </c>
+      <c r="AF19">
+        <v>1.67</v>
+      </c>
+      <c r="AG19">
+        <v>2.1</v>
+      </c>
+      <c r="AH19">
         <v>4.25</v>
       </c>
-      <c r="O19">
-        <v>1.58</v>
-      </c>
-      <c r="P19">
-        <v>6.5</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1.5</v>
-      </c>
-      <c r="S19">
-        <v>2.5</v>
-      </c>
-      <c r="T19">
-        <v>3.56</v>
-      </c>
-      <c r="U19">
-        <v>1.29</v>
-      </c>
-      <c r="V19">
-        <v>9</v>
-      </c>
-      <c r="W19">
-        <v>1.03</v>
-      </c>
-      <c r="X19">
-        <v>1.1</v>
-      </c>
-      <c r="Y19">
-        <v>6.95</v>
-      </c>
-      <c r="Z19">
-        <v>1.51</v>
-      </c>
-      <c r="AA19">
-        <v>2.4</v>
-      </c>
-      <c r="AB19">
-        <v>2.6</v>
-      </c>
-      <c r="AC19">
-        <v>1.47</v>
-      </c>
-      <c r="AD19">
-        <v>4.95</v>
-      </c>
-      <c r="AE19">
-        <v>1.16</v>
-      </c>
-      <c r="AF19">
-        <v>2.2</v>
-      </c>
-      <c r="AG19">
-        <v>1.6</v>
-      </c>
-      <c r="AH19">
-        <v>10.5</v>
-      </c>
       <c r="AI19">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M20">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O20">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P20">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S20">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U20">
+        <v>1.29</v>
+      </c>
+      <c r="V20">
+        <v>9</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.1</v>
+      </c>
+      <c r="Y20">
+        <v>6.95</v>
+      </c>
+      <c r="Z20">
+        <v>1.52</v>
+      </c>
+      <c r="AA20">
+        <v>2.4</v>
+      </c>
+      <c r="AB20">
+        <v>2.3</v>
+      </c>
+      <c r="AC20">
         <v>1.5</v>
       </c>
-      <c r="V20">
-        <v>6</v>
-      </c>
-      <c r="W20">
-        <v>1.13</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>9.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.2</v>
-      </c>
-      <c r="AA20">
-        <v>4.33</v>
-      </c>
-      <c r="AB20">
-        <v>1.7</v>
-      </c>
-      <c r="AC20">
-        <v>2.1</v>
-      </c>
       <c r="AD20">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AH20">
-        <v>4.25</v>
+        <v>10.5</v>
       </c>
       <c r="AI20">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3092,10 +3092,10 @@
         <v>1.85</v>
       </c>
       <c r="M21">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
         <v>1.67</v>
@@ -3131,16 +3131,16 @@
         <v>6.35</v>
       </c>
       <c r="Z21">
+        <v>1.53</v>
+      </c>
+      <c r="AA21">
+        <v>2.25</v>
+      </c>
+      <c r="AB21">
+        <v>2.33</v>
+      </c>
+      <c r="AC21">
         <v>1.48</v>
-      </c>
-      <c r="AA21">
-        <v>2.48</v>
-      </c>
-      <c r="AB21">
-        <v>2.75</v>
-      </c>
-      <c r="AC21">
-        <v>1.55</v>
       </c>
       <c r="AD21">
         <v>4.75</v>
@@ -3205,13 +3205,13 @@
         <v>116</v>
       </c>
       <c r="L22">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="M22">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O22">
         <v>2.15</v>
@@ -3253,10 +3253,10 @@
         <v>2.5</v>
       </c>
       <c r="AB22">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AC22">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD22">
         <v>4.3</v>
@@ -3321,13 +3321,13 @@
         <v>116</v>
       </c>
       <c r="L23">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="M23">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="N23">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="O23">
         <v>1.73</v>
@@ -3363,16 +3363,16 @@
         <v>5.7</v>
       </c>
       <c r="Z23">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AA23">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB23">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AD23">
         <v>6.41</v>
@@ -3437,13 +3437,13 @@
         <v>116</v>
       </c>
       <c r="L24">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="M24">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="N24">
-        <v>2.61</v>
+        <v>4.7</v>
       </c>
       <c r="O24">
         <v>1.8</v>
@@ -3485,10 +3485,10 @@
         <v>3.3</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD24">
         <v>3.3</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3553,13 +3553,13 @@
         <v>116</v>
       </c>
       <c r="L25">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M25">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="O25">
         <v>1.9</v>
@@ -3601,10 +3601,10 @@
         <v>2.53</v>
       </c>
       <c r="AB25">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD25">
         <v>4.6</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -172,27 +172,27 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
@@ -232,42 +232,42 @@
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Botoşani</t>
   </si>
   <si>
-    <t>Gnistan</t>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
     <t>Videoton</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
+    <t>Montana</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Montana</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
@@ -280,12 +280,12 @@
     <t>Avaí</t>
   </si>
   <si>
+    <t>Tombense</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Tombense</t>
-  </si>
-  <si>
     <t>Atlanta</t>
   </si>
   <si>
@@ -301,42 +301,42 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>HJK</t>
+  </si>
+  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
-    <t>HJK</t>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
     <t>Primorje</t>
   </si>
   <si>
+    <t>Lokomotiv Plovdiv</t>
+  </si>
+  <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Lokomotiv Plovdiv</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -349,10 +349,10 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Brusque</t>
-  </si>
-  <si>
-    <t>Maringá</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
@@ -1093,7 +1093,7 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>72</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P4">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q4">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V4">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AA4">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AF4">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI4">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1209,7 +1209,7 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -1233,76 +1233,76 @@
         <v>116</v>
       </c>
       <c r="L5">
-        <v>4.1</v>
+        <v>1.79</v>
       </c>
       <c r="M5">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="N5">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P5">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="T5">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="U5">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V5">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z5">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA5">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="AB5">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AD5">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE5">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AG5">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AH5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI5">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ5" t="s">
         <v>117</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
@@ -1349,37 +1349,37 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N6">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P6">
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
         <v>1.38</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="U6">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1394,31 +1394,31 @@
         <v>1.3</v>
       </c>
       <c r="AA6">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AB6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE6">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH6">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1697,76 +1697,76 @@
         <v>116</v>
       </c>
       <c r="L9">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N9">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="s">
         <v>117</v>
@@ -1786,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>69</v>
@@ -1902,16 +1902,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,76 +1929,76 @@
         <v>116</v>
       </c>
       <c r="L11">
+        <v>2.65</v>
+      </c>
+      <c r="M11">
+        <v>3.3</v>
+      </c>
+      <c r="N11">
+        <v>2.55</v>
+      </c>
+      <c r="O11">
         <v>2</v>
       </c>
-      <c r="M11">
+      <c r="P11">
+        <v>9</v>
+      </c>
+      <c r="Q11">
+        <v>2.05</v>
+      </c>
+      <c r="R11">
+        <v>1.38</v>
+      </c>
+      <c r="S11">
+        <v>2.8</v>
+      </c>
+      <c r="T11">
+        <v>2.75</v>
+      </c>
+      <c r="U11">
+        <v>1.4</v>
+      </c>
+      <c r="V11">
+        <v>7.5</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.06</v>
+      </c>
+      <c r="Y11">
+        <v>9</v>
+      </c>
+      <c r="Z11">
+        <v>1.3</v>
+      </c>
+      <c r="AA11">
         <v>3.45</v>
       </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11">
-        <v>1.8</v>
-      </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-      <c r="Q11">
-        <v>2.1</v>
-      </c>
-      <c r="R11">
-        <v>1.35</v>
-      </c>
-      <c r="S11">
-        <v>3.1</v>
-      </c>
-      <c r="T11">
-        <v>2.5</v>
-      </c>
-      <c r="U11">
-        <v>1.43</v>
-      </c>
-      <c r="V11">
-        <v>6.2</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>11</v>
-      </c>
-      <c r="Z11">
-        <v>1.2</v>
-      </c>
-      <c r="AA11">
-        <v>3.75</v>
-      </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC11">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AD11">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AE11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH11">
-        <v>5.47</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,16 +2018,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="M12">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2161,13 +2161,13 @@
         <v>116</v>
       </c>
       <c r="L13">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M13">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N13">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O13">
         <v>1.91</v>
@@ -2366,10 +2366,10 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
@@ -2393,76 +2393,76 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>1.12</v>
+        <v>3.21</v>
       </c>
       <c r="M15">
-        <v>7.68</v>
+        <v>2.98</v>
       </c>
       <c r="N15">
-        <v>12</v>
+        <v>2.12</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="P15">
-        <v>26</v>
+        <v>7.1</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="V15">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="Z15">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AA15">
-        <v>7.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB15">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="AD15">
-        <v>1.6</v>
+        <v>4.27</v>
       </c>
       <c r="AE15">
-        <v>2.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>2.33</v>
+        <v>9.5</v>
       </c>
       <c r="AI15">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2482,10 +2482,10 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
@@ -2509,76 +2509,76 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>3.21</v>
+        <v>1.12</v>
       </c>
       <c r="M16">
-        <v>2.98</v>
+        <v>7.68</v>
       </c>
       <c r="N16">
-        <v>2.12</v>
+        <v>12</v>
       </c>
       <c r="O16">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>7.1</v>
+        <v>26</v>
       </c>
       <c r="Q16">
+        <v>4.2</v>
+      </c>
+      <c r="R16">
+        <v>1.13</v>
+      </c>
+      <c r="S16">
+        <v>5</v>
+      </c>
+      <c r="T16">
+        <v>1.65</v>
+      </c>
+      <c r="U16">
+        <v>2.05</v>
+      </c>
+      <c r="V16">
+        <v>3.2</v>
+      </c>
+      <c r="W16">
+        <v>1.3</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>41</v>
+      </c>
+      <c r="Z16">
+        <v>1.03</v>
+      </c>
+      <c r="AA16">
+        <v>7.5</v>
+      </c>
+      <c r="AB16">
+        <v>1.25</v>
+      </c>
+      <c r="AC16">
+        <v>3.75</v>
+      </c>
+      <c r="AD16">
+        <v>1.6</v>
+      </c>
+      <c r="AE16">
+        <v>2.14</v>
+      </c>
+      <c r="AF16">
         <v>1.73</v>
       </c>
-      <c r="R16">
-        <v>1.44</v>
-      </c>
-      <c r="S16">
-        <v>2.45</v>
-      </c>
-      <c r="T16">
-        <v>3.2</v>
-      </c>
-      <c r="U16">
-        <v>1.3</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>1.04</v>
-      </c>
-      <c r="X16">
-        <v>1.08</v>
-      </c>
-      <c r="Y16">
-        <v>7.5</v>
-      </c>
-      <c r="Z16">
-        <v>1.38</v>
-      </c>
-      <c r="AA16">
-        <v>2.63</v>
-      </c>
-      <c r="AB16">
-        <v>2.2</v>
-      </c>
-      <c r="AC16">
-        <v>1.55</v>
-      </c>
-      <c r="AD16">
-        <v>4.27</v>
-      </c>
-      <c r="AE16">
-        <v>1.18</v>
-      </c>
-      <c r="AF16">
-        <v>1.95</v>
-      </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>9.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI16">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="s">
         <v>117</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -3089,70 +3089,70 @@
         <v>116</v>
       </c>
       <c r="L21">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="M21">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="O21">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P21">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q21">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R21">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S21">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
         <v>1.27</v>
       </c>
       <c r="V21">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>6.35</v>
+        <v>6.6</v>
       </c>
       <c r="Z21">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AD21">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AE21">
         <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH21">
         <v>9</v>
@@ -3205,70 +3205,70 @@
         <v>116</v>
       </c>
       <c r="L22">
-        <v>2.56</v>
+        <v>1.85</v>
       </c>
       <c r="M22">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="N22">
-        <v>2.67</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="P22">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="R22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S22">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
         <v>1.27</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>6.6</v>
+        <v>6.35</v>
       </c>
       <c r="Z22">
+        <v>1.53</v>
+      </c>
+      <c r="AA22">
+        <v>2.25</v>
+      </c>
+      <c r="AB22">
+        <v>2.33</v>
+      </c>
+      <c r="AC22">
         <v>1.48</v>
       </c>
-      <c r="AA22">
-        <v>2.5</v>
-      </c>
-      <c r="AB22">
-        <v>2.2</v>
-      </c>
-      <c r="AC22">
-        <v>1.55</v>
-      </c>
       <c r="AD22">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AE22">
         <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AH22">
         <v>9</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -172,45 +172,45 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
+    <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -232,54 +232,54 @@
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Botoşani</t>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
   </si>
   <si>
     <t>Odra Opole</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>GKS Katowice</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
+    <t>Koper</t>
   </si>
   <si>
     <t>Videoton</t>
   </si>
   <si>
-    <t>Koper</t>
+    <t>B36</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
-    <t>B36</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Tombense</t>
   </si>
   <si>
@@ -301,52 +301,52 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>HJK</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Trelleborg</t>
+  </si>
+  <si>
+    <t>Varberg</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
-  </si>
-  <si>
-    <t>Trelleborg</t>
-  </si>
-  <si>
-    <t>Varberg</t>
+    <t>Primorje</t>
   </si>
   <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Primorje</t>
+    <t>TB</t>
   </si>
   <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>TB</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
   </si>
   <si>
     <t>Maringá</t>
@@ -891,7 +891,7 @@
         <v>3.02</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="O2">
         <v>1.57</v>
@@ -906,16 +906,16 @@
         <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="T2">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -924,34 +924,34 @@
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>6.62</v>
       </c>
       <c r="Z2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AA2">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AB2">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AC2">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AD2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF2">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AG2">
         <v>1.66</v>
       </c>
       <c r="AH2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI2">
         <v>1.01</v>
@@ -1025,7 +1025,7 @@
         <v>2.4</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U3">
         <v>1.29</v>
@@ -1055,19 +1055,19 @@
         <v>1.53</v>
       </c>
       <c r="AD3">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF3">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG3">
         <v>1.76</v>
       </c>
       <c r="AH3">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI3">
         <v>1.01</v>
@@ -1093,7 +1093,7 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>72</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>4.1</v>
+        <v>1.79</v>
       </c>
       <c r="M4">
-        <v>3.65</v>
+        <v>3.21</v>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="Q4">
-        <v>1.57</v>
+        <v>2.71</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z4">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="AB4">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AD4">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE4">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AG4">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI4">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -1209,7 +1209,7 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -1233,76 +1233,76 @@
         <v>116</v>
       </c>
       <c r="L5">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="M5">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="O5">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q5">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="U5">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>7.4</v>
+        <v>5.25</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AC5">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="AD5">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AF5">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI5">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>117</v>
@@ -1349,76 +1349,76 @@
         <v>116</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="M6">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>2.99</v>
       </c>
       <c r="O6">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>117</v>
@@ -1465,13 +1465,13 @@
         <v>116</v>
       </c>
       <c r="L7">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
         <v>1.4</v>
@@ -1489,52 +1489,52 @@
         <v>3.8</v>
       </c>
       <c r="T7">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
         <v>4</v>
       </c>
       <c r="W7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AA7">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="AB7">
         <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AD7">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE7">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AI7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AJ7" t="s">
         <v>117</v>
@@ -1581,40 +1581,40 @@
         <v>116</v>
       </c>
       <c r="L8">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="M8">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N8">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="O8">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.05</v>
@@ -1623,34 +1623,34 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA8">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB8">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD8">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI8">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>117</v>
@@ -1670,10 +1670,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>77</v>
@@ -1697,76 +1697,76 @@
         <v>116</v>
       </c>
       <c r="L9">
+        <v>2.65</v>
+      </c>
+      <c r="M9">
+        <v>3.3</v>
+      </c>
+      <c r="N9">
+        <v>2.55</v>
+      </c>
+      <c r="O9">
         <v>2</v>
       </c>
-      <c r="M9">
+      <c r="P9">
+        <v>9</v>
+      </c>
+      <c r="Q9">
+        <v>2.05</v>
+      </c>
+      <c r="R9">
+        <v>1.38</v>
+      </c>
+      <c r="S9">
+        <v>2.8</v>
+      </c>
+      <c r="T9">
+        <v>2.75</v>
+      </c>
+      <c r="U9">
+        <v>1.4</v>
+      </c>
+      <c r="V9">
+        <v>7.5</v>
+      </c>
+      <c r="W9">
+        <v>1.08</v>
+      </c>
+      <c r="X9">
+        <v>1.06</v>
+      </c>
+      <c r="Y9">
+        <v>9</v>
+      </c>
+      <c r="Z9">
+        <v>1.3</v>
+      </c>
+      <c r="AA9">
         <v>3.45</v>
       </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9">
-        <v>1.8</v>
-      </c>
-      <c r="P9">
-        <v>10</v>
-      </c>
-      <c r="Q9">
-        <v>2.1</v>
-      </c>
-      <c r="R9">
-        <v>1.35</v>
-      </c>
-      <c r="S9">
-        <v>3.1</v>
-      </c>
-      <c r="T9">
-        <v>2.5</v>
-      </c>
-      <c r="U9">
-        <v>1.43</v>
-      </c>
-      <c r="V9">
-        <v>6.2</v>
-      </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
-      <c r="Y9">
-        <v>11</v>
-      </c>
-      <c r="Z9">
-        <v>1.2</v>
-      </c>
-      <c r="AA9">
-        <v>3.75</v>
-      </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC9">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AD9">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AE9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH9">
-        <v>5.47</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="s">
         <v>117</v>
@@ -1786,16 +1786,16 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1813,52 +1813,52 @@
         <v>116</v>
       </c>
       <c r="L10">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="M10">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="N10">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="O10">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P10">
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
         <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T10">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V10">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AB10">
         <v>1.76</v>
@@ -1867,22 +1867,22 @@
         <v>1.94</v>
       </c>
       <c r="AD10">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AE10">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AI10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="s">
         <v>117</v>
@@ -1902,16 +1902,16 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,43 +1929,43 @@
         <v>116</v>
       </c>
       <c r="L11">
-        <v>2.65</v>
+        <v>3.21</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N11">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P11">
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S11">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V11">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1974,31 +1974,31 @@
         <v>1.3</v>
       </c>
       <c r="AA11">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AB11">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD11">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AE11">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
         <v>117</v>
@@ -2018,16 +2018,16 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2045,76 +2045,76 @@
         <v>116</v>
       </c>
       <c r="L12">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M12">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC12">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ12" t="s">
         <v>117</v>
@@ -2161,64 +2161,64 @@
         <v>116</v>
       </c>
       <c r="L13">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M13">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N13">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>1.67</v>
+      </c>
+      <c r="AC13">
         <v>2.1</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>1.9</v>
-      </c>
-      <c r="AC13">
-        <v>1.9</v>
-      </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2277,22 +2277,22 @@
         <v>116</v>
       </c>
       <c r="L14">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="M14">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>2.85</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2325,16 +2325,16 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -2366,10 +2366,10 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
@@ -2393,76 +2393,76 @@
         <v>116</v>
       </c>
       <c r="L15">
-        <v>3.21</v>
+        <v>1.14</v>
       </c>
       <c r="M15">
-        <v>2.98</v>
+        <v>7.2</v>
       </c>
       <c r="N15">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="O15">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>7.1</v>
+        <v>26</v>
       </c>
       <c r="Q15">
+        <v>4.2</v>
+      </c>
+      <c r="R15">
+        <v>1.14</v>
+      </c>
+      <c r="S15">
+        <v>4.75</v>
+      </c>
+      <c r="T15">
         <v>1.73</v>
       </c>
-      <c r="R15">
-        <v>1.44</v>
-      </c>
-      <c r="S15">
-        <v>2.45</v>
-      </c>
-      <c r="T15">
+      <c r="U15">
+        <v>2</v>
+      </c>
+      <c r="V15">
         <v>3.2</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>1.3</v>
       </c>
-      <c r="V15">
-        <v>9</v>
-      </c>
-      <c r="W15">
-        <v>1.04</v>
-      </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y15">
+        <v>36</v>
+      </c>
+      <c r="Z15">
+        <v>1.03</v>
+      </c>
+      <c r="AA15">
         <v>7.5</v>
       </c>
-      <c r="Z15">
-        <v>1.38</v>
-      </c>
-      <c r="AA15">
-        <v>2.63</v>
-      </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC15">
-        <v>1.55</v>
+        <v>3.73</v>
       </c>
       <c r="AD15">
-        <v>4.27</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH15">
-        <v>9.5</v>
+        <v>2.41</v>
       </c>
       <c r="AI15">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AJ15" t="s">
         <v>117</v>
@@ -2482,10 +2482,10 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>83</v>
@@ -2509,76 +2509,76 @@
         <v>116</v>
       </c>
       <c r="L16">
-        <v>1.12</v>
+        <v>3.21</v>
       </c>
       <c r="M16">
-        <v>7.68</v>
+        <v>2.98</v>
       </c>
       <c r="N16">
-        <v>12</v>
+        <v>2.12</v>
       </c>
       <c r="O16">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="P16">
-        <v>26</v>
+        <v>7.1</v>
       </c>
       <c r="Q16">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="T16">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="V16">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="W16">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>41</v>
+        <v>7.1</v>
       </c>
       <c r="Z16">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AA16">
-        <v>7.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB16">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="AD16">
-        <v>1.6</v>
+        <v>4.32</v>
       </c>
       <c r="AE16">
-        <v>2.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH16">
-        <v>2.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI16">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AJ16" t="s">
         <v>117</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>
@@ -2741,13 +2741,13 @@
         <v>116</v>
       </c>
       <c r="L18">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M18">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O18">
         <v>1.55</v>
@@ -2759,13 +2759,13 @@
         <v>2.42</v>
       </c>
       <c r="R18">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S18">
         <v>4.1</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
         <v>1.69</v>
@@ -2777,28 +2777,28 @@
         <v>1.18</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z18">
         <v>1.1</v>
       </c>
       <c r="AA18">
-        <v>5.61</v>
+        <v>5.7</v>
       </c>
       <c r="AB18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC18">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AD18">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AE18">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AF18">
         <v>1.45</v>
@@ -2857,76 +2857,76 @@
         <v>116</v>
       </c>
       <c r="L19">
-        <v>5.25</v>
+        <v>1.66</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="O19">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="P19">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q19">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S19">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
+        <v>1.29</v>
+      </c>
+      <c r="V19">
+        <v>9</v>
+      </c>
+      <c r="W19">
+        <v>1.03</v>
+      </c>
+      <c r="X19">
+        <v>1.1</v>
+      </c>
+      <c r="Y19">
+        <v>6.25</v>
+      </c>
+      <c r="Z19">
         <v>1.5</v>
       </c>
-      <c r="V19">
-        <v>6</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.2</v>
-      </c>
       <c r="AA19">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AD19">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="AE19">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AH19">
-        <v>4.25</v>
+        <v>10</v>
       </c>
       <c r="AI19">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AJ19" t="s">
         <v>117</v>
@@ -2973,76 +2973,76 @@
         <v>116</v>
       </c>
       <c r="L20">
-        <v>1.66</v>
+        <v>5.25</v>
       </c>
       <c r="M20">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N20">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
+        <v>1.3</v>
+      </c>
+      <c r="S20">
+        <v>3.4</v>
+      </c>
+      <c r="T20">
+        <v>2.5</v>
+      </c>
+      <c r="U20">
         <v>1.5</v>
       </c>
-      <c r="S20">
+      <c r="V20">
+        <v>6</v>
+      </c>
+      <c r="W20">
+        <v>1.13</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>9.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.2</v>
+      </c>
+      <c r="AA20">
+        <v>4.33</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
+        <v>2.1</v>
+      </c>
+      <c r="AD20">
         <v>2.5</v>
       </c>
-      <c r="T20">
-        <v>3.56</v>
-      </c>
-      <c r="U20">
-        <v>1.29</v>
-      </c>
-      <c r="V20">
-        <v>9</v>
-      </c>
-      <c r="W20">
-        <v>1.03</v>
-      </c>
-      <c r="X20">
-        <v>1.1</v>
-      </c>
-      <c r="Y20">
-        <v>6.95</v>
-      </c>
-      <c r="Z20">
-        <v>1.52</v>
-      </c>
-      <c r="AA20">
-        <v>2.4</v>
-      </c>
-      <c r="AB20">
-        <v>2.3</v>
-      </c>
-      <c r="AC20">
+      <c r="AE20">
         <v>1.5</v>
       </c>
-      <c r="AD20">
-        <v>4.95</v>
-      </c>
-      <c r="AE20">
-        <v>1.16</v>
-      </c>
       <c r="AF20">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>10.5</v>
+        <v>4.25</v>
       </c>
       <c r="AI20">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="s">
         <v>117</v>
@@ -3107,34 +3107,34 @@
         <v>2.02</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S21">
         <v>2.5</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z21">
         <v>1.48</v>
       </c>
       <c r="AA21">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AB21">
         <v>2.2</v>
@@ -3146,7 +3146,7 @@
         <v>4.3</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
         <v>2</v>
@@ -3158,7 +3158,7 @@
         <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ21" t="s">
         <v>117</v>
@@ -3226,16 +3226,16 @@
         <v>1.53</v>
       </c>
       <c r="S22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>1.27</v>
       </c>
       <c r="V22">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="W22">
         <v>1.04</v>
@@ -3244,7 +3244,7 @@
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>1.53</v>
@@ -3259,10 +3259,10 @@
         <v>1.48</v>
       </c>
       <c r="AD22">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
         <v>1.97</v>
@@ -3351,10 +3351,10 @@
         <v>1.18</v>
       </c>
       <c r="V23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
         <v>1.13</v>
@@ -3369,13 +3369,13 @@
         <v>2.38</v>
       </c>
       <c r="AB23">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AC23">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD23">
-        <v>6.41</v>
+        <v>6.58</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
@@ -3455,22 +3455,22 @@
         <v>2.3</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S24">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T24">
         <v>2.93</v>
       </c>
       <c r="U24">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V24">
         <v>7</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -3482,7 +3482,7 @@
         <v>1.35</v>
       </c>
       <c r="AA24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB24">
         <v>1.96</v>
@@ -3497,7 +3497,7 @@
         <v>1.36</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG24">
         <v>1.93</v>
@@ -3506,7 +3506,7 @@
         <v>6.5</v>
       </c>
       <c r="AI24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AJ24" t="s">
         <v>117</v>
@@ -3526,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>69</v>
@@ -3571,22 +3571,22 @@
         <v>2.4</v>
       </c>
       <c r="R25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S25">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T25">
         <v>3.3</v>
       </c>
       <c r="U25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V25">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.1</v>
@@ -3598,7 +3598,7 @@
         <v>1.5</v>
       </c>
       <c r="AA25">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB25">
         <v>2.25</v>
@@ -3607,16 +3607,16 @@
         <v>1.5</v>
       </c>
       <c r="AD25">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH25">
         <v>8.699999999999999</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -169,12 +169,12 @@
     <t>Russia FNL</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Botoşani</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Botoşani</t>
-  </si>
-  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -298,10 +298,10 @@
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>Slavia Sofia</t>
-  </si>
-  <si>
-    <t>Unirea Slobozia</t>
   </si>
   <si>
     <t>HJK</t>
@@ -1001,76 +1001,76 @@
         <v>116</v>
       </c>
       <c r="L3">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M3">
+        <v>3.21</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3">
+        <v>1.66</v>
+      </c>
+      <c r="P3">
+        <v>7.5</v>
+      </c>
+      <c r="Q3">
+        <v>2.71</v>
+      </c>
+      <c r="R3">
+        <v>1.44</v>
+      </c>
+      <c r="S3">
+        <v>2.59</v>
+      </c>
+      <c r="T3">
+        <v>3.04</v>
+      </c>
+      <c r="U3">
+        <v>1.33</v>
+      </c>
+      <c r="V3">
+        <v>7.4</v>
+      </c>
+      <c r="W3">
+        <v>1.03</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>7.5</v>
+      </c>
+      <c r="Z3">
+        <v>1.33</v>
+      </c>
+      <c r="AA3">
         <v>2.84</v>
       </c>
-      <c r="N3">
-        <v>2.4</v>
-      </c>
-      <c r="O3">
-        <v>2.34</v>
-      </c>
-      <c r="P3">
-        <v>6.4</v>
-      </c>
-      <c r="Q3">
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>1.61</v>
+      </c>
+      <c r="AD3">
+        <v>3.6</v>
+      </c>
+      <c r="AE3">
+        <v>1.21</v>
+      </c>
+      <c r="AF3">
         <v>1.92</v>
       </c>
-      <c r="R3">
-        <v>1.45</v>
-      </c>
-      <c r="S3">
-        <v>2.4</v>
-      </c>
-      <c r="T3">
-        <v>3.34</v>
-      </c>
-      <c r="U3">
-        <v>1.29</v>
-      </c>
-      <c r="V3">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W3">
-        <v>1.05</v>
-      </c>
-      <c r="X3">
-        <v>1.06</v>
-      </c>
-      <c r="Y3">
-        <v>6.25</v>
-      </c>
-      <c r="Z3">
-        <v>1.44</v>
-      </c>
-      <c r="AA3">
-        <v>2.55</v>
-      </c>
-      <c r="AB3">
-        <v>2.25</v>
-      </c>
-      <c r="AC3">
-        <v>1.53</v>
-      </c>
-      <c r="AD3">
-        <v>4</v>
-      </c>
-      <c r="AE3">
-        <v>1.19</v>
-      </c>
-      <c r="AF3">
-        <v>2</v>
-      </c>
       <c r="AG3">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AH3">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
         <v>117</v>
@@ -1117,76 +1117,76 @@
         <v>116</v>
       </c>
       <c r="L4">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N4">
+        <v>2.4</v>
+      </c>
+      <c r="O4">
+        <v>2.34</v>
+      </c>
+      <c r="P4">
+        <v>6.4</v>
+      </c>
+      <c r="Q4">
+        <v>1.92</v>
+      </c>
+      <c r="R4">
+        <v>1.45</v>
+      </c>
+      <c r="S4">
+        <v>2.4</v>
+      </c>
+      <c r="T4">
+        <v>3.34</v>
+      </c>
+      <c r="U4">
+        <v>1.29</v>
+      </c>
+      <c r="V4">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.06</v>
+      </c>
+      <c r="Y4">
+        <v>6.25</v>
+      </c>
+      <c r="Z4">
+        <v>1.44</v>
+      </c>
+      <c r="AA4">
+        <v>2.55</v>
+      </c>
+      <c r="AB4">
+        <v>2.25</v>
+      </c>
+      <c r="AC4">
+        <v>1.53</v>
+      </c>
+      <c r="AD4">
         <v>4</v>
       </c>
-      <c r="O4">
-        <v>1.66</v>
-      </c>
-      <c r="P4">
-        <v>7.5</v>
-      </c>
-      <c r="Q4">
-        <v>2.71</v>
-      </c>
-      <c r="R4">
-        <v>1.44</v>
-      </c>
-      <c r="S4">
-        <v>2.59</v>
-      </c>
-      <c r="T4">
-        <v>3.04</v>
-      </c>
-      <c r="U4">
-        <v>1.33</v>
-      </c>
-      <c r="V4">
-        <v>7.4</v>
-      </c>
-      <c r="W4">
-        <v>1.03</v>
-      </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
-      <c r="Y4">
-        <v>7.5</v>
-      </c>
-      <c r="Z4">
-        <v>1.33</v>
-      </c>
-      <c r="AA4">
-        <v>2.84</v>
-      </c>
-      <c r="AB4">
-        <v>2.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.61</v>
-      </c>
-      <c r="AD4">
-        <v>3.6</v>
-      </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH4">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AI4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="s">
         <v>117</v>
@@ -2482,7 +2482,7 @@
         <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>68</v>
@@ -2598,7 +2598,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
         <v>68</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -657,20 +657,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -747,12 +747,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '45+3', '90+4']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '50']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>2.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W3" t="n">
         <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>5.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.18</v>
       </c>
-      <c r="AA4" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>4.76</v>
       </c>
       <c r="M5" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.21</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>2.07</v>
+        <v>3.11</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.38</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.6</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
         <v>5.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>2.07</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>2.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,64 +2126,64 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.21</v>
+        <v>3.97</v>
       </c>
       <c r="M16" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2540,10 +2540,10 @@
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
         <v>3.2</v>
@@ -2555,16 +2555,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AA16" t="n">
         <v>2.67</v>
@@ -2573,25 +2573,25 @@
         <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
         <v>2.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH16" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.55</v>
@@ -2804,58 +2804,58 @@
         <v>2.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AA18" t="n">
         <v>5.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
         <v>1.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.52</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="O20" t="n">
         <v>1.58</v>
@@ -3068,49 +3068,49 @@
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.35</v>
       </c>
       <c r="AG20" t="n">
         <v>1.58</v>
@@ -3119,7 +3119,7 @@
         <v>10</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="N21" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
         <v>2.15</v>
@@ -3200,58 +3200,58 @@
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
         <v>4.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="n">
         <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
         <v>1.67</v>
@@ -3332,58 +3332,58 @@
         <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
         <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AE22" t="n">
         <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
         <v>1.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.73</v>
@@ -3464,7 +3464,7 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
@@ -3473,37 +3473,37 @@
         <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
         <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.47</v>
+        <v>6.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
         <v>2.5</v>
@@ -3512,10 +3512,10 @@
         <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.32</v>
+        <v>3.43</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.8</v>
@@ -3596,13 +3596,13 @@
         <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
         <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
         <v>1.37</v>
@@ -3614,40 +3614,40 @@
         <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
         <v>1.36</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH24" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="M25" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>1.9</v>
@@ -3728,52 +3728,52 @@
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
         <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AC25" t="n">
         <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="n">
         <v>8.699999999999999</v>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -789,20 +789,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '34', '64', '88']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -921,20 +921,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '57']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1053,20 +1053,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '81']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '54', '65', '74']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1185,20 +1185,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '62', '90+3', '90+5']</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '14', '20']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1308,19 +1308,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1330,89 +1330,89 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.33</v>
       </c>
-      <c r="S7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="AF7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH7" t="n">
         <v>6.5</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>1.11</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '78']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,106 +1572,106 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.38</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '49', '90+4']</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,111 +1704,111 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="M10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD10" t="n">
         <v>3.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '81']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '45']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1845,20 +1845,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '27', '35', '65', '75', '79']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '85']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,111 +1968,111 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '43']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2109,20 +2109,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '68']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2244,17 +2244,17 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '29', '62']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2354,121 +2354,121 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.14</v>
+        <v>3.97</v>
       </c>
       <c r="M15" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="O15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.22</v>
       </c>
-      <c r="P15" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AL15" s="3" t="n">
@@ -2486,29 +2486,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2518,80 +2518,80 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.97</v>
+        <v>1.12</v>
       </c>
       <c r="M16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>13</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y16" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.300000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '84']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -902,32 +902,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>4.76</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="P4" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.38</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.56</v>
       </c>
-      <c r="AD4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>['45+1', '57']</t>
+          <t>['57', '81']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['38', '54', '65', '74']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1070,85 +1070,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.76</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.7</v>
+        <v>2.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>['57', '81']</t>
+          <t>['45+1', '57']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>['38', '54', '65', '74']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1166,121 +1166,121 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="N6" t="n">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.73</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>['19', '62', '90+3', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>['4', '14', '20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1449,102 +1449,102 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '81']</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '45']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1694,35 +1694,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,43 +1730,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.73</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>10</v>
@@ -1775,40 +1775,40 @@
         <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>['54', '81']</t>
+          <t>['19', '62', '90+3', '90+5']</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>['15', '45']</t>
+          <t>['4', '14', '20']</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,22 +1836,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1862,85 +1862,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.98</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.08</v>
+        <v>6.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['17', '27', '35', '65', '75', '79']</t>
+          <t>['13', '43']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>['9', '85']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,22 +1968,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1994,85 +1994,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="T12" t="n">
-        <v>3.02</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>7.75</v>
+        <v>3.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>['13', '43']</t>
+          <t>['17', '27', '35', '65', '75', '79']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['9', '85']</t>
         </is>
       </c>
       <c r="AL12" s="3" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,111 +2100,111 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AG13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>['35', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '29', '62']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,25 +2232,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2258,85 +2258,85 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>['35', '68']</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>['13', '29', '62']</t>
         </is>
       </c>
       <c r="AL14" s="3" t="n">
@@ -2637,20 +2637,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87', '90+1']</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
@@ -2769,20 +2769,20 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '70', '75', '84']</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AL18" s="3" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>5.15</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.58</v>
@@ -3068,43 +3068,43 @@
         <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W20" t="n">
         <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>1.15</v>
@@ -3113,13 +3113,13 @@
         <v>2.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="N21" t="n">
         <v>2.66</v>
@@ -3200,16 +3200,16 @@
         <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
         <v>10</v>
@@ -3218,34 +3218,34 @@
         <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
         <v>7.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
         <v>2.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="n">
         <v>9</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="O22" t="n">
         <v>1.67</v>
@@ -3332,58 +3332,58 @@
         <v>2.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="U22" t="n">
         <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
         <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.9</v>
@@ -3728,58 +3728,58 @@
         <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
         <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA25" t="n">
         <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD25" t="n">
         <v>4.8</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG25" t="n">
         <v>1.75</v>
       </c>
       <c r="AH25" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL25"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -683,13 +678,13 @@
         <v>3.83</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="P2" t="n">
-        <v>8.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>5.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
@@ -704,58 +699,55 @@
         <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.7</v>
+        <v>2.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.53</v>
+        <v>4.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['22', '45+3', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['26', '50']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['22', '45+3', '90+4']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['26', '50']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45866.4375</v>
       </c>
     </row>
@@ -770,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -806,88 +798,85 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>7.4</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>2.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.84</v>
+        <v>4.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['45+1', '57']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.92</v>
       </c>
-      <c r="AG3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['2', '34', '64', '88']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45866.54166666666</v>
       </c>
     </row>
@@ -902,124 +891,121 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.61</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['2', '34', '64', '88']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG4" t="n">
-        <v>2.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>['57', '81']</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['38', '54', '65', '74']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45866.54166666666</v>
       </c>
     </row>
@@ -1034,26 +1020,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1070,88 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['18', '47', '78']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>['45+1', '57']</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>['5']</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45866.54166666666</v>
       </c>
     </row>
@@ -1161,130 +1144,127 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.07</v>
+        <v>4.76</v>
       </c>
       <c r="M6" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.99</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.35</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['57', '81']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['38', '54', '65', '74']</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>45866.58333333334</v>
+        <v>2.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>45866.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1334,88 +1314,85 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="M7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.3</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.92</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['54', '78']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.33</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH7" t="n">
-        <v>6.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>['54', '78']</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -1430,124 +1407,121 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>['54', '81']</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>['15', '45']</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -1562,124 +1536,121 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="M9" t="n">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>['17', '49', '90+4']</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -1694,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1730,88 +1701,85 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>5.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.22</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>2.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AC10" t="n">
         <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['15', '72', '76']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>['19', '62', '90+3', '90+5']</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>['4', '14', '20']</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -1871,13 +1839,13 @@
         <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
@@ -1892,58 +1860,55 @@
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>7.75</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>2.97</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['13', '43']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>['13', '43']</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -2003,13 +1968,13 @@
         <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>17</v>
+        <v>2.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -2024,58 +1989,55 @@
         <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>6.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.12</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['17', '27', '35', '65', '75', '79']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['9', '85']</t>
+        </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>['17', '27', '35', '65', '75', '79']</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>['9', '85']</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45866.58333333334</v>
       </c>
     </row>
@@ -2085,40 +2047,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,89 +2088,86 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.949999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['19', '62', '90+3', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['4', '14', '20']</t>
+        </is>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.75</v>
+        <v>1.77</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>['13', '29', '62']</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
-        <v>45866.625</v>
+        <v>1.73</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45866.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2222,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,114 +2191,111 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['13', '29', '62']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.52</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AI14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>['35', '68']</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45866.625</v>
       </c>
     </row>
@@ -2349,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2390,89 +2346,86 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.97</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>4.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>4.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['35', '68']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
-        <v>45866.63541666666</v>
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45866.625</v>
       </c>
     </row>
     <row r="16">
@@ -2481,37 +2434,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2522,89 +2475,86 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
-        <v>7.5</v>
+        <v>3.98</v>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>36</v>
+        <v>1.67</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.03</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.94</v>
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['35', '68']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>['52', '84']</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>45866.63541666666</v>
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45866.625</v>
       </c>
     </row>
     <row r="17">
@@ -2613,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2654,89 +2604,86 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>3.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.73</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>['87', '90+1']</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>45866.64583333334</v>
+      <c r="AK17" s="3" t="n">
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="18">
@@ -2745,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2786,89 +2733,86 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="M18" t="n">
-        <v>4.26</v>
+        <v>7.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.42</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['52', '84']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>['53', '70', '75', '84']</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>45866.67708333334</v>
+      <c r="AJ18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45866.63541666666</v>
       </c>
     </row>
     <row r="19">
@@ -2877,130 +2821,127 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.25</v>
+        <v>2.09</v>
       </c>
       <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.53</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['87', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.25</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>45866.79166666666</v>
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45866.64583333334</v>
       </c>
     </row>
     <row r="20">
@@ -3009,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,115 +2965,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.48</v>
+        <v>4.26</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P20" t="n">
-        <v>6.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>3.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.1</v>
+        <v>5.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF20" t="n">
         <v>2.4</v>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['53', '70', '75', '84']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
       <c r="AG20" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>45866.79166666666</v>
+        <v>1.55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45866.67708333334</v>
       </c>
     </row>
     <row r="21">
@@ -3141,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,115 +3094,112 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
         <v>2.55</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V21" t="n">
-        <v>10</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y21" t="n">
-        <v>7.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z21" t="n">
         <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.43</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.4</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AD21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['9', '13', '39', '45+2', '88']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>45866.8125</v>
+        <v>1.58</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3273,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,115 +3223,112 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>5.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.64</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.67</v>
       </c>
-      <c r="P22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V22" t="n">
-        <v>11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="AD22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['13', '22', '44', '76']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI22" t="n">
         <v>2.6</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>45866.8125</v>
+      <c r="AJ22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45866.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3405,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,19 +3352,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3442,93 +3374,90 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.91</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>2.43</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>4.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>12.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>45866.88194444445</v>
+        <v>2.15</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3537,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,115 +3481,112 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="M24" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" t="n">
         <v>2.3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Z24" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['35', '41', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
-        <v>45866.88541666666</v>
+        <v>1.67</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45866.8125</v>
       </c>
     </row>
     <row r="25">
@@ -3669,129 +3595,384 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['30', '36']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45866.88194444445</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['51', '59']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['9', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>45866.88541666666</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>2.3</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>2.98</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>3.2</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.9</v>
       </c>
-      <c r="P25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.4</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AK27" s="3" t="n">
         <v>45866.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-28.xlsx
+++ b/jogos_2025-07-28.xlsx
@@ -762,26 +762,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['45+1', '57']</t>
+          <t>['18', '47', '78']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45866.54166666666</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.49</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['45+1', '57']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.92</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['2', '34', '64', '88']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.71</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45866.54166666666</v>
@@ -1020,35 +1020,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['18', '47', '78']</t>
+          <t>['2', '34', '64', '88']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45866.54166666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.49</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['19', '62', '90+3', '90+5']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['54', '78']</t>
+          <t>['4', '14', '20']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45866.58333333334</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '43']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45866.58333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,91 +1675,91 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['15', '72', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45866.58333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3.2</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['13', '43']</t>
+          <t>['54', '81']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['15', '45']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45866.58333333334</v>
@@ -1923,35 +1923,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="n">
         <v>4.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>6.5</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['17', '27', '35', '65', '75', '79']</t>
+          <t>['15', '72', '76']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['9', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45866.58333333334</v>
@@ -2052,119 +2052,119 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.11</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2.5</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['19', '62', '90+3', '90+5']</t>
+          <t>['17', '27', '35', '65', '75', '79']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['4', '14', '20']</t>
+          <t>['9', '85']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45866.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['35', '68']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['13', '29', '62']</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45866.625</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['13', '29', '62']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.52</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AI16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['35', '68']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45866.625</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="U23" t="n">
         <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['35', '41', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AI23" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45866.8125</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>3.64</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
         <v>1.27</v>
       </c>
       <c r="V24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['35', '41', '90+6']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45866.8125</v>
